--- a/SPC26S1 - 04 April v2.xlsx
+++ b/SPC26S1 - 04 April v2.xlsx
@@ -1037,7 +1037,7 @@
     <t>Cells you edit</t>
   </si>
   <si>
-    <t>Four columns are shaded pale yellow and are the ones meant to be edited here: Claim Status (A), Notes (B), Processed Date (C) and Latest Date Worked (K). Claim Status has a drop-down of the statuses already in use - it is a suggestion, not a restriction, so you can type anything.</t>
+    <t>Four columns are shaded pale yellow and are the ones meant to be edited here: Claim Status (A), Notes (B), Processed Date (C) and Latest Date Worked (K). Claim Status has a drop-down list, and anything not on the list is rejected so a typo cannot slip in. To add a new status, edit the list under Data &gt; Data Validation.</t>
   </si>
   <si>
     <t>Example of the expected format - Claim Status: "Denied";  Notes: "Corrected service line 1 - resubmitted";  Processed Date: "06/25/2026";  Latest Date Worked: "08/12/2026".</t>
@@ -2318,7 +2318,7 @@
     <t xml:space="preserve">Waiting for Bri's reply - Juan sent MR to me </t>
   </si>
   <si>
-    <t>Statuses currently in use: Denied, Finalized, PAID, Pending, Received, Rejected, Under Review.</t>
+    <t>Statuses on the drop-down: Denied, Finalized, Not found, PAID, Pending, Received, Rejected, Under Review.</t>
   </si>
   <si>
     <t>540 days</t>
@@ -2330,7 +2330,7 @@
     <t>Every specialty sheet is sorted in four groups: Rejected claims at the very top, then claims with an empty Latest Date Worked (column K), then the other open claims, and Finalized and PAID claims at the bottom (a Finalized or PAID claim with an empty Latest Date Worked stays in the empty Latest Date Worked group). Within each group, rows are ordered by how close the claim is to its primary payer's timely filing deadline. Days Until Deadline (column L) carries the count: five days or less left is shaded red, a negative number means the filing window has already closed, and a blank means no limit is on file for that payer.</t>
   </si>
   <si>
-    <t>Deadline order within each group, with the colour band each row gets, counted on 19 September 2026:</t>
+    <t>Deadline order within each group, with the colour band each row gets (these counts update automatically):</t>
   </si>
   <si>
     <t xml:space="preserve">    1 - Due in 5 days or less: 0</t>
@@ -2342,7 +2342,7 @@
     <t xml:space="preserve">    3 - Due in 31+ days: 24</t>
   </si>
   <si>
-    <t>'SPC26S1 - 00 Master v2.xlsx' (same folder) holds all 477 claims for 2026 S1. Its Claim Status and Notes columns are formulas that read this file, so anything you type in columns A and B here shows up there. Keep both files in the same folder, keep the file name unchanged, and save this file before opening the master.</t>
+    <t>'SPC26S1 - 00 Master v2.xlsx' (same folder) holds every claim for 2026 S1. Its Claim Status and Notes columns are formulas that read this file, so anything you type in columns A and B here shows up there. Keep both files in the same folder, keep the file name unchanged, and save this file before opening the master.</t>
   </si>
   <si>
     <t>93923 x1; 93970 x1</t>
@@ -3919,8 +3919,9 @@
       <c r="A2" s="9"/>
     </row>
     <row r="3" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A3" s="9" t="s">
-        <v>438</v>
+      <c r="A3" s="9" t="str">
+        <f>COUNTA(BH!$D$2:$D$1000,DME!$D$2:$D$1000,GAE!$D$2:$D$1000,ORTHO!$D$2:$D$1000,US!$D$2:$D$1000)&amp;" claims with a date of service in 2026-04 April, split into one sheet per specialty: BH, DME, GAE, ORTHO, US."</f>
+        <v>84 claims with a date of service in 2026-04 April, split into one sheet per specialty: BH, DME, GAE, ORTHO, US.</v>
       </c>
     </row>
     <row r="4" spans="1:1" x14ac:dyDescent="0.25">
@@ -3942,28 +3943,33 @@
       </c>
     </row>
     <row r="8" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A8" s="9" t="s">
-        <v>441</v>
+      <c r="A8" s="9" t="str">
+        <f>"    1 - Due in 5 days or less: "&amp;SUM(COUNTIFS(BH!$L$2:$L$1000,"&gt;=0",BH!$L$2:$L$1000,"&lt;=5"),COUNTIFS(DME!$L$2:$L$1000,"&gt;=0",DME!$L$2:$L$1000,"&lt;=5"),COUNTIFS(GAE!$L$2:$L$1000,"&gt;=0",GAE!$L$2:$L$1000,"&lt;=5"),COUNTIFS(ORTHO!$L$2:$L$1000,"&gt;=0",ORTHO!$L$2:$L$1000,"&lt;=5"),COUNTIFS(US!$L$2:$L$1000,"&gt;=0",US!$L$2:$L$1000,"&lt;=5"))</f>
+        <v>    1 - Due in 5 days or less: 0</v>
       </c>
     </row>
     <row r="9" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A9" s="9" t="s">
-        <v>442</v>
+      <c r="A9" s="9" t="str">
+        <f>"    2 - Due in 6-30 days: "&amp;SUM(COUNTIFS(BH!$L$2:$L$1000,"&gt;5",BH!$L$2:$L$1000,"&lt;=30"),COUNTIFS(DME!$L$2:$L$1000,"&gt;5",DME!$L$2:$L$1000,"&lt;=30"),COUNTIFS(GAE!$L$2:$L$1000,"&gt;5",GAE!$L$2:$L$1000,"&lt;=30"),COUNTIFS(ORTHO!$L$2:$L$1000,"&gt;5",ORTHO!$L$2:$L$1000,"&lt;=30"),COUNTIFS(US!$L$2:$L$1000,"&gt;5",US!$L$2:$L$1000,"&lt;=30"))</f>
+        <v>    2 - Due in 6-30 days: 1</v>
       </c>
     </row>
     <row r="10" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A10" s="9" t="s">
-        <v>443</v>
+      <c r="A10" s="9" t="str">
+        <f>"    3 - Due in 31+ days: "&amp;SUM(COUNTIFS(BH!$L$2:$L$1000,"&gt;30"),COUNTIFS(DME!$L$2:$L$1000,"&gt;30"),COUNTIFS(GAE!$L$2:$L$1000,"&gt;30"),COUNTIFS(ORTHO!$L$2:$L$1000,"&gt;30"),COUNTIFS(US!$L$2:$L$1000,"&gt;30"))</f>
+        <v>    3 - Due in 31+ days: 24</v>
       </c>
     </row>
     <row r="11" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A11" s="9" t="s">
-        <v>2</v>
+      <c r="A11" s="9" t="str">
+        <f>"    4 - Past deadline: "&amp;SUM(COUNTIFS(BH!$L$2:$L$1000,"&lt;0"),COUNTIFS(DME!$L$2:$L$1000,"&lt;0"),COUNTIFS(GAE!$L$2:$L$1000,"&lt;0"),COUNTIFS(ORTHO!$L$2:$L$1000,"&lt;0"),COUNTIFS(US!$L$2:$L$1000,"&lt;0"))</f>
+        <v>    4 - Past deadline: 51</v>
       </c>
     </row>
     <row r="12" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A12" s="9" t="s">
-        <v>3</v>
+      <c r="A12" s="9" t="str">
+        <f>"    5 - No limit on file: "&amp;SUM(COUNTIFS(BH!$D$2:$D$1000,"&lt;&gt;",BH!$L$2:$L$1000,""),COUNTIFS(DME!$D$2:$D$1000,"&lt;&gt;",DME!$L$2:$L$1000,""),COUNTIFS(GAE!$D$2:$D$1000,"&lt;&gt;",GAE!$L$2:$L$1000,""),COUNTIFS(ORTHO!$D$2:$D$1000,"&lt;&gt;",ORTHO!$L$2:$L$1000,""),COUNTIFS(US!$D$2:$D$1000,"&lt;&gt;",US!$L$2:$L$1000,""))</f>
+        <v>    5 - No limit on file: 8</v>
       </c>
     </row>
     <row r="13" spans="1:1" x14ac:dyDescent="0.25">
@@ -5636,8 +5642,8 @@
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="1">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" promptTitle="Claim Status" prompt="Pick a status, or type a new one." sqref="A2:A12" xr:uid="{00000000-0002-0000-0000-000000000000}">
-      <formula1>"Denied,Finalized,PAID,Pending,Received,Rejected,Under Review"</formula1>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorStyle="stop" errorTitle="Claim Status" error="Choose a status from the drop-down list. To add a new status, edit the list under Data &gt; Data Validation." promptTitle="Claim Status" prompt="Pick a status from the list." sqref="A2:A1000">
+      <formula1>"Denied,Finalized,Not found,PAID,Pending,Received,Rejected,Under Review"</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -9389,8 +9395,8 @@
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="1">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" promptTitle="Claim Status" prompt="Pick a status, or type a new one." sqref="A2:A32" xr:uid="{00000000-0002-0000-0100-000000000000}">
-      <formula1>"Denied,Finalized,PAID,Pending,Received,Rejected,Under Review"</formula1>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorStyle="stop" errorTitle="Claim Status" error="Choose a status from the drop-down list. To add a new status, edit the list under Data &gt; Data Validation." promptTitle="Claim Status" prompt="Pick a status from the list." sqref="A2:A1000">
+      <formula1>"Denied,Finalized,Not found,PAID,Pending,Received,Rejected,Under Review"</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -10364,8 +10370,8 @@
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="1">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" promptTitle="Claim Status" prompt="Pick a status, or type a new one." sqref="A2:A7" xr:uid="{00000000-0002-0000-0200-000000000000}">
-      <formula1>"Denied,Finalized,PAID,Pending,Received,Rejected,Under Review"</formula1>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorStyle="stop" errorTitle="Claim Status" error="Choose a status from the drop-down list. To add a new status, edit the list under Data &gt; Data Validation." promptTitle="Claim Status" prompt="Pick a status from the list." sqref="A2:A1000">
+      <formula1>"Denied,Finalized,Not found,PAID,Pending,Received,Rejected,Under Review"</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -12529,8 +12535,8 @@
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="1">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" promptTitle="Claim Status" prompt="Pick a status, or type a new one." sqref="A2:A18" xr:uid="{00000000-0002-0000-0300-000000000000}">
-      <formula1>"Denied,Finalized,PAID,Pending,Received,Rejected,Under Review"</formula1>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorStyle="stop" errorTitle="Claim Status" error="Choose a status from the drop-down list. To add a new status, edit the list under Data &gt; Data Validation." promptTitle="Claim Status" prompt="Pick a status from the list." sqref="A2:A1000">
+      <formula1>"Denied,Finalized,Not found,PAID,Pending,Received,Rejected,Under Review"</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -14924,8 +14930,8 @@
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="1">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" promptTitle="Claim Status" prompt="Pick a status, or type a new one." sqref="A2:A20" xr:uid="{00000000-0002-0000-0400-000000000000}">
-      <formula1>"Denied,Finalized,PAID,Pending,Received,Rejected,Under Review"</formula1>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorStyle="stop" errorTitle="Claim Status" error="Choose a status from the drop-down list. To add a new status, edit the list under Data &gt; Data Validation." promptTitle="Claim Status" prompt="Pick a status from the list." sqref="A2:A1000">
+      <formula1>"Denied,Finalized,Not found,PAID,Pending,Received,Rejected,Under Review"</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/SPC26S1 - 04 April v2.xlsx
+++ b/SPC26S1 - 04 April v2.xlsx
@@ -2522,7 +2522,7 @@
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="108">
+  <dxfs count="109">
     <dxf>
       <font>
         <color rgb="FF1F4E79"/>
@@ -3572,9 +3572,13 @@
       </fill>
     </dxf>
     <dxf>
+      <font>
+        <b/>
+        <color rgb="FF000000"/>
+      </font>
       <fill>
         <patternFill patternType="solid">
-          <bgColor rgb="FFF8CBAD"/>
+          <bgColor rgb="FFFF9933"/>
         </patternFill>
       </fill>
     </dxf>
@@ -3596,6 +3600,13 @@
       <fill>
         <patternFill patternType="solid">
           <bgColor rgb="FFBFBFBF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFCE4E4"/>
         </patternFill>
       </fill>
     </dxf>
@@ -3904,7 +3915,7 @@
   <sheetPr>
     <tabColor rgb="FF1F4E79"/>
   </sheetPr>
-  <dimension ref="A1:A49"/>
+  <dimension ref="A1:A50"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="118" customWidth="1"/>
@@ -4133,14 +4144,14 @@
     <row r="45" spans="1:1">
       <c r="A45" s="9" t="inlineStr">
         <is>
-          <t xml:space="preserve">    Under Review - orange</t>
+          <t xml:space="preserve">    Under Review - bright orange, bold (follow up on these)</t>
         </is>
       </c>
     </row>
     <row r="46" spans="1:1">
       <c r="A46" s="9" t="inlineStr">
         <is>
-          <t xml:space="preserve">    Denied - red</t>
+          <t xml:space="preserve">    Denied, not worked yet (Latest Date Worked empty) - red</t>
         </is>
       </c>
     </row>
@@ -4161,6 +4172,13 @@
     <row r="49" spans="1:1">
       <c r="A49" s="9" t="inlineStr">
         <is>
+          <t xml:space="preserve">    Denied, already worked (Latest Date Worked filled in) - light pink</t>
+        </is>
+      </c>
+    </row>
+    <row r="50" spans="1:1">
+      <c r="A50" s="9" t="inlineStr">
+        <is>
           <t xml:space="preserve">Any other status is left unshaded.</t>
         </is>
       </c>
@@ -4203,6 +4221,11 @@
   </conditionalFormatting>
   <conditionalFormatting sqref="A48">
     <cfRule type="expression" dxfId="107" priority="8">
+      <formula>TRUE</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A49">
+    <cfRule type="expression" dxfId="108" priority="9">
       <formula>TRUE</formula>
     </cfRule>
   </conditionalFormatting>
@@ -5632,7 +5655,10 @@
       <formula>TRIM($A2)="Under Review"</formula>
     </cfRule>
     <cfRule type="expression" dxfId="105" priority="26">
-      <formula>TRIM($A2)="Denied"</formula>
+      <formula>AND(TRIM($A2)="Denied",$K2="")</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="108" priority="29">
+      <formula>AND(TRIM($A2)="Denied",$K2&lt;&gt;"")</formula>
     </cfRule>
     <cfRule type="expression" dxfId="106" priority="27">
       <formula>TRIM($A2)="Rejected"</formula>
@@ -9385,7 +9411,10 @@
       <formula>TRIM($A2)="Under Review"</formula>
     </cfRule>
     <cfRule type="expression" dxfId="105" priority="26">
-      <formula>TRIM($A2)="Denied"</formula>
+      <formula>AND(TRIM($A2)="Denied",$K2="")</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="108" priority="29">
+      <formula>AND(TRIM($A2)="Denied",$K2&lt;&gt;"")</formula>
     </cfRule>
     <cfRule type="expression" dxfId="106" priority="27">
       <formula>TRIM($A2)="Rejected"</formula>
@@ -10360,7 +10389,10 @@
       <formula>TRIM($A2)="Under Review"</formula>
     </cfRule>
     <cfRule type="expression" dxfId="105" priority="26">
-      <formula>TRIM($A2)="Denied"</formula>
+      <formula>AND(TRIM($A2)="Denied",$K2="")</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="108" priority="29">
+      <formula>AND(TRIM($A2)="Denied",$K2&lt;&gt;"")</formula>
     </cfRule>
     <cfRule type="expression" dxfId="106" priority="27">
       <formula>TRIM($A2)="Rejected"</formula>
@@ -12525,7 +12557,10 @@
       <formula>TRIM($A2)="Under Review"</formula>
     </cfRule>
     <cfRule type="expression" dxfId="105" priority="26">
-      <formula>TRIM($A2)="Denied"</formula>
+      <formula>AND(TRIM($A2)="Denied",$K2="")</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="108" priority="29">
+      <formula>AND(TRIM($A2)="Denied",$K2&lt;&gt;"")</formula>
     </cfRule>
     <cfRule type="expression" dxfId="106" priority="27">
       <formula>TRIM($A2)="Rejected"</formula>
@@ -14920,7 +14955,10 @@
       <formula>TRIM($A2)="Under Review"</formula>
     </cfRule>
     <cfRule type="expression" dxfId="105" priority="26">
-      <formula>TRIM($A2)="Denied"</formula>
+      <formula>AND(TRIM($A2)="Denied",$K2="")</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="108" priority="29">
+      <formula>AND(TRIM($A2)="Denied",$K2&lt;&gt;"")</formula>
     </cfRule>
     <cfRule type="expression" dxfId="106" priority="27">
       <formula>TRIM($A2)="Rejected"</formula>

--- a/SPC26S1 - 04 April v2.xlsx
+++ b/SPC26S1 - 04 April v2.xlsx
@@ -2330,7 +2330,7 @@
     <t>Every specialty sheet is sorted in four groups: Rejected claims at the very top, then claims with an empty Latest Date Worked (column K), then the other open claims, and Finalized and PAID claims at the bottom (a Finalized or PAID claim with an empty Latest Date Worked stays in the empty Latest Date Worked group). Within each group, rows are ordered by how close the claim is to its primary payer's timely filing deadline. Days Until Deadline (column L) carries the count: five days or less left is shaded red, a negative number means the filing window has already closed, and a blank means no limit is on file for that payer.</t>
   </si>
   <si>
-    <t>Deadline order within each group, with the colour band each row gets (these counts update automatically):</t>
+    <t>Deadline order within each group, with the colour band each row gets (these counts update automatically; Finalized claims with a Latest Date Worked have their deadline cells left empty and are not counted):</t>
   </si>
   <si>
     <t xml:space="preserve">    1 - Due in 5 days or less: 0</t>
@@ -3962,24 +3962,24 @@
     <row r="9" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A9" s="9" t="str">
         <f>"    2 - Due in 6-30 days: "&amp;SUM(COUNTIFS(BH!$L$2:$L$1000,"&gt;5",BH!$L$2:$L$1000,"&lt;=30"),COUNTIFS(DME!$L$2:$L$1000,"&gt;5",DME!$L$2:$L$1000,"&lt;=30"),COUNTIFS(GAE!$L$2:$L$1000,"&gt;5",GAE!$L$2:$L$1000,"&lt;=30"),COUNTIFS(ORTHO!$L$2:$L$1000,"&gt;5",ORTHO!$L$2:$L$1000,"&lt;=30"),COUNTIFS(US!$L$2:$L$1000,"&gt;5",US!$L$2:$L$1000,"&lt;=30"))</f>
-        <v>    2 - Due in 6-30 days: 1</v>
+        <v>    2 - Due in 6-30 days: 0</v>
       </c>
     </row>
     <row r="10" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A10" s="9" t="str">
         <f>"    3 - Due in 31+ days: "&amp;SUM(COUNTIFS(BH!$L$2:$L$1000,"&gt;30"),COUNTIFS(DME!$L$2:$L$1000,"&gt;30"),COUNTIFS(GAE!$L$2:$L$1000,"&gt;30"),COUNTIFS(ORTHO!$L$2:$L$1000,"&gt;30"),COUNTIFS(US!$L$2:$L$1000,"&gt;30"))</f>
-        <v>    3 - Due in 31+ days: 24</v>
+        <v>    3 - Due in 31+ days: 21</v>
       </c>
     </row>
     <row r="11" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A11" s="9" t="str">
         <f>"    4 - Past deadline: "&amp;SUM(COUNTIFS(BH!$L$2:$L$1000,"&lt;0"),COUNTIFS(DME!$L$2:$L$1000,"&lt;0"),COUNTIFS(GAE!$L$2:$L$1000,"&lt;0"),COUNTIFS(ORTHO!$L$2:$L$1000,"&lt;0"),COUNTIFS(US!$L$2:$L$1000,"&lt;0"))</f>
-        <v>    4 - Past deadline: 51</v>
+        <v>    4 - Past deadline: 38</v>
       </c>
     </row>
     <row r="12" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A12" s="9" t="str">
-        <f>"    5 - No limit on file: "&amp;SUM(COUNTIFS(BH!$D$2:$D$1000,"&lt;&gt;",BH!$L$2:$L$1000,""),COUNTIFS(DME!$D$2:$D$1000,"&lt;&gt;",DME!$L$2:$L$1000,""),COUNTIFS(GAE!$D$2:$D$1000,"&lt;&gt;",GAE!$L$2:$L$1000,""),COUNTIFS(ORTHO!$D$2:$D$1000,"&lt;&gt;",ORTHO!$L$2:$L$1000,""),COUNTIFS(US!$D$2:$D$1000,"&lt;&gt;",US!$L$2:$L$1000,""))</f>
+        <f>"    5 - No limit on file: "&amp;SUM(SUMPRODUCT((BH!$D$2:$D$1000&lt;&gt;"")*(BH!$L$2:$L$1000="")*(1-(TRIM(BH!$A$2:$A$1000)="Finalized")*(BH!$K$2:$K$1000&lt;&gt;""))),SUMPRODUCT((DME!$D$2:$D$1000&lt;&gt;"")*(DME!$L$2:$L$1000="")*(1-(TRIM(DME!$A$2:$A$1000)="Finalized")*(DME!$K$2:$K$1000&lt;&gt;""))),SUMPRODUCT((GAE!$D$2:$D$1000&lt;&gt;"")*(GAE!$L$2:$L$1000="")*(1-(TRIM(GAE!$A$2:$A$1000)="Finalized")*(GAE!$K$2:$K$1000&lt;&gt;""))),SUMPRODUCT((ORTHO!$D$2:$D$1000&lt;&gt;"")*(ORTHO!$L$2:$L$1000="")*(1-(TRIM(ORTHO!$A$2:$A$1000)="Finalized")*(ORTHO!$K$2:$K$1000&lt;&gt;""))),SUMPRODUCT((US!$D$2:$D$1000&lt;&gt;"")*(US!$L$2:$L$1000="")*(1-(TRIM(US!$A$2:$A$1000)="Finalized")*(US!$K$2:$K$1000&lt;&gt;""))))</f>
         <v>    5 - No limit on file: 8</v>
       </c>
     </row>
@@ -4432,14 +4432,15 @@
         <v>198</v>
       </c>
       <c r="M2" s="12" t="str">
-        <f ca="1">IF($C2="","",$C2+365-TODAY())</f>
+        <f ca="1">IF(AND(TRIM($A2)="Finalized",$K2&lt;&gt;""),"",IF($C2="","",$C2+365-TODAY()))</f>
         <v/>
       </c>
       <c r="N2" s="12" t="str">
-        <f ca="1">IF($C2="","",$C2+120-TODAY())</f>
+        <f ca="1">IF(AND(TRIM($A2)="Finalized",$K2&lt;&gt;""),"",IF($C2="","",$C2+120-TODAY()))</f>
         <v/>
       </c>
       <c r="O2" s="6">
+        <f>IF(AND(TRIM($A2)="Finalized",$K2&lt;&gt;""),"",DATE(2027,4,21))</f>
         <v>46498</v>
       </c>
       <c r="P2" s="5" t="s">
@@ -4719,14 +4720,15 @@
         <v>178</v>
       </c>
       <c r="M5" s="12">
-        <f ca="1">IF($C5="","",$C5+365-TODAY())</f>
+        <f ca="1">IF(AND(TRIM($A5)="Finalized",$K5&lt;&gt;""),"",IF($C5="","",$C5+365-TODAY()))</f>
         <v>222</v>
       </c>
       <c r="N5" s="12">
-        <f ca="1">IF($C5="","",$C5+120-TODAY())</f>
+        <f ca="1">IF(AND(TRIM($A5)="Finalized",$K5&lt;&gt;""),"",IF($C5="","",$C5+120-TODAY()))</f>
         <v>-23</v>
       </c>
       <c r="O5" s="6">
+        <f>IF(AND(TRIM($A5)="Finalized",$K5&lt;&gt;""),"",DATE(2027,4,1))</f>
         <v>46478</v>
       </c>
       <c r="P5" s="5" t="s">
@@ -4830,14 +4832,15 @@
         <v>-97</v>
       </c>
       <c r="M6" s="12">
-        <f ca="1">IF($F6="","",$F6+90-TODAY())</f>
+        <f ca="1">IF(AND(TRIM($A6)="Finalized",$K6&lt;&gt;""),"",IF($F6="","",$F6+90-TODAY()))</f>
         <v>-97</v>
       </c>
       <c r="N6" s="12">
-        <f ca="1">IF($C6="","",$C6+365-TODAY())</f>
+        <f ca="1">IF(AND(TRIM($A6)="Finalized",$K6&lt;&gt;""),"",IF($C6="","",$C6+365-TODAY()))</f>
         <v>227</v>
       </c>
       <c r="O6" s="6">
+        <f>IF(AND(TRIM($A6)="Finalized",$K6&lt;&gt;""),"",DATE(2026,6,30))</f>
         <v>46203</v>
       </c>
       <c r="P6" s="5" t="s">
@@ -4941,14 +4944,15 @@
         <v>-83</v>
       </c>
       <c r="M7" s="12">
-        <f ca="1">IF($C7="","",$C7+365-TODAY())</f>
+        <f ca="1">IF(AND(TRIM($A7)="Finalized",$K7&lt;&gt;""),"",IF($C7="","",$C7+365-TODAY()))</f>
         <v>327</v>
       </c>
       <c r="N7" s="12">
-        <f ca="1">IF($C7="","",$C7+365-TODAY())</f>
+        <f ca="1">IF(AND(TRIM($A7)="Finalized",$K7&lt;&gt;""),"",IF($C7="","",$C7+365-TODAY()))</f>
         <v>327</v>
       </c>
       <c r="O7" s="6">
+        <f>IF(AND(TRIM($A7)="Finalized",$K7&lt;&gt;""),"",DATE(2026,7,14))</f>
         <v>46217</v>
       </c>
       <c r="P7" s="5" t="s">
@@ -5050,14 +5054,15 @@
         <v>-78</v>
       </c>
       <c r="M8" s="12">
-        <f ca="1">IF($F8="","",$F8+90-TODAY())</f>
+        <f ca="1">IF(AND(TRIM($A8)="Finalized",$K8&lt;&gt;""),"",IF($F8="","",$F8+90-TODAY()))</f>
         <v>-78</v>
       </c>
       <c r="N8" s="12">
-        <f ca="1">IF($C8="","",$C8+365-TODAY())</f>
+        <f ca="1">IF(AND(TRIM($A8)="Finalized",$K8&lt;&gt;""),"",IF($C8="","",$C8+365-TODAY()))</f>
         <v>222</v>
       </c>
       <c r="O8" s="6">
+        <f>IF(AND(TRIM($A8)="Finalized",$K8&lt;&gt;""),"",DATE(2026,7,19))</f>
         <v>46222</v>
       </c>
       <c r="P8" s="5" t="s">
@@ -5161,14 +5166,15 @@
         <v>-76</v>
       </c>
       <c r="M9" s="12">
-        <f ca="1">IF($C9="","",$C9+365-TODAY())</f>
+        <f ca="1">IF(AND(TRIM($A9)="Finalized",$K9&lt;&gt;""),"",IF($C9="","",$C9+365-TODAY()))</f>
         <v>232</v>
       </c>
       <c r="N9" s="12">
-        <f ca="1">IF($C9="","",$C9+365-TODAY())</f>
+        <f ca="1">IF(AND(TRIM($A9)="Finalized",$K9&lt;&gt;""),"",IF($C9="","",$C9+365-TODAY()))</f>
         <v>232</v>
       </c>
       <c r="O9" s="6">
+        <f>IF(AND(TRIM($A9)="Finalized",$K9&lt;&gt;""),"",DATE(2026,7,21))</f>
         <v>46224</v>
       </c>
       <c r="P9" s="5" t="s">
@@ -5274,14 +5280,15 @@
         <v>-74</v>
       </c>
       <c r="M10" s="12">
-        <f ca="1">IF($C10="","",$C10+365-TODAY())</f>
+        <f ca="1">IF(AND(TRIM($A10)="Finalized",$K10&lt;&gt;""),"",IF($C10="","",$C10+365-TODAY()))</f>
         <v>232</v>
       </c>
       <c r="N10" s="12">
-        <f ca="1">IF($C10="","",$C10+365-TODAY())</f>
+        <f ca="1">IF(AND(TRIM($A10)="Finalized",$K10&lt;&gt;""),"",IF($C10="","",$C10+365-TODAY()))</f>
         <v>232</v>
       </c>
       <c r="O10" s="6">
+        <f>IF(AND(TRIM($A10)="Finalized",$K10&lt;&gt;""),"",DATE(2026,7,23))</f>
         <v>46226</v>
       </c>
       <c r="P10" s="5" t="s">
@@ -5385,14 +5392,15 @@
         <v>-60</v>
       </c>
       <c r="M11" s="12">
-        <f ca="1">IF($C11="","",$C11+365-TODAY())</f>
+        <f ca="1">IF(AND(TRIM($A11)="Finalized",$K11&lt;&gt;""),"",IF($C11="","",$C11+365-TODAY()))</f>
         <v>226</v>
       </c>
       <c r="N11" s="12">
-        <f ca="1">IF($C11="","",$C11+90-TODAY())</f>
+        <f ca="1">IF(AND(TRIM($A11)="Finalized",$K11&lt;&gt;""),"",IF($C11="","",$C11+90-TODAY()))</f>
         <v>-49</v>
       </c>
       <c r="O11" s="6">
+        <f>IF(AND(TRIM($A11)="Finalized",$K11&lt;&gt;""),"",DATE(2026,8,6))</f>
         <v>46240</v>
       </c>
       <c r="P11" s="5" t="s">
@@ -5489,20 +5497,21 @@
       <c r="K12" s="3">
         <v>46265</v>
       </c>
-      <c r="L12" s="12">
+      <c t="str" r="L12" s="12">
         <f ca="1">IF($O12="","",$O12-TODAY())</f>
-        <v>-75</v>
-      </c>
-      <c r="M12" s="12">
-        <f ca="1">IF($F12="","",$F12+90-TODAY())</f>
-        <v>-75</v>
-      </c>
-      <c r="N12" s="12">
-        <f ca="1">IF($C12="","",$C12+540-TODAY())</f>
-        <v>397</v>
-      </c>
-      <c r="O12" s="6">
-        <v>46225</v>
+        <v/>
+      </c>
+      <c t="str" r="M12" s="12">
+        <f ca="1">IF(AND(TRIM($A12)="Finalized",$K12&lt;&gt;""),"",IF($F12="","",$F12+90-TODAY()))</f>
+        <v/>
+      </c>
+      <c t="str" r="N12" s="12">
+        <f ca="1">IF(AND(TRIM($A12)="Finalized",$K12&lt;&gt;""),"",IF($C12="","",$C12+540-TODAY()))</f>
+        <v/>
+      </c>
+      <c t="str" r="O12" s="6">
+        <f>IF(AND(TRIM($A12)="Finalized",$K12&lt;&gt;""),"",DATE(2026,7,22))</f>
+        <v/>
       </c>
       <c r="P12" s="5" t="s">
         <v>87</v>
@@ -5570,100 +5579,105 @@
     </row>
   </sheetData>
   <autoFilter ref="A1:AN12" xr:uid="{00000000-0009-0000-0000-000000000000}"/>
+  <conditionalFormatting sqref="L2:O1000">
+    <cfRule type="expression" dxfId="101" priority="1" stopIfTrue="1">
+      <formula>AND(TRIM($A2)="Finalized",$K2&lt;&gt;"")</formula>
+    </cfRule>
+  </conditionalFormatting>
   <conditionalFormatting sqref="L2:L12">
-    <cfRule type="expression" dxfId="99" priority="1">
+    <cfRule type="expression" dxfId="99" priority="2">
       <formula>AND($L2&lt;&gt;"", $L2&gt;=0, $L2&lt;=5)</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="98" priority="2">
+    <cfRule type="expression" dxfId="98" priority="3">
       <formula>AND($L2&lt;&gt;"", $L2&gt;5, $L2&lt;=30)</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="97" priority="3">
+    <cfRule type="expression" dxfId="97" priority="4">
       <formula>AND($L2&lt;&gt;"", $L2&gt;30)</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="96" priority="4">
+    <cfRule type="expression" dxfId="96" priority="5">
       <formula>AND($L2&lt;&gt;"", $L2&lt;0)</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="95" priority="5">
+    <cfRule type="expression" dxfId="95" priority="6">
       <formula>$L2=""</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="M2:M12">
-    <cfRule type="expression" dxfId="94" priority="6">
+    <cfRule type="expression" dxfId="94" priority="7">
       <formula>AND($M2&lt;&gt;"", $M2&gt;=0, $M2&lt;=5)</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="93" priority="7">
+    <cfRule type="expression" dxfId="93" priority="8">
       <formula>AND($M2&lt;&gt;"", $M2&gt;5, $M2&lt;=30)</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="92" priority="8">
+    <cfRule type="expression" dxfId="92" priority="9">
       <formula>AND($M2&lt;&gt;"", $M2&gt;30)</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="91" priority="9">
+    <cfRule type="expression" dxfId="91" priority="10">
       <formula>AND($M2&lt;&gt;"", $M2&lt;0)</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="90" priority="10">
+    <cfRule type="expression" dxfId="90" priority="11">
       <formula>$M2=""</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="N2:N12">
-    <cfRule type="expression" dxfId="89" priority="11">
+    <cfRule type="expression" dxfId="89" priority="12">
       <formula>AND($N2&lt;&gt;"", $N2&gt;=0, $N2&lt;=5)</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="88" priority="12">
+    <cfRule type="expression" dxfId="88" priority="13">
       <formula>AND($N2&lt;&gt;"", $N2&gt;5, $N2&lt;=30)</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="87" priority="13">
+    <cfRule type="expression" dxfId="87" priority="14">
       <formula>AND($N2&lt;&gt;"", $N2&gt;30)</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="86" priority="14">
+    <cfRule type="expression" dxfId="86" priority="15">
       <formula>AND($N2&lt;&gt;"", $N2&lt;0)</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="85" priority="15">
+    <cfRule type="expression" dxfId="85" priority="16">
       <formula>$N2=""</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="O2:U12">
-    <cfRule type="expression" dxfId="84" priority="16">
+    <cfRule type="expression" dxfId="84" priority="17">
       <formula>AND($L2&lt;&gt;"", $L2&gt;=0, $L2&lt;=5)</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="83" priority="17">
+    <cfRule type="expression" dxfId="83" priority="18">
       <formula>AND($L2&lt;&gt;"", $L2&gt;5, $L2&lt;=30)</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="82" priority="18">
+    <cfRule type="expression" dxfId="82" priority="19">
       <formula>AND($L2&lt;&gt;"", $L2&gt;30)</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="81" priority="19">
+    <cfRule type="expression" dxfId="81" priority="20">
       <formula>AND($L2&lt;&gt;"", $L2&lt;0)</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="80" priority="20">
+    <cfRule type="expression" dxfId="80" priority="21">
       <formula>$L2=""</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A2:AN1000">
-    <cfRule type="expression" dxfId="100" priority="21">
+    <cfRule type="expression" dxfId="100" priority="22">
       <formula>TRIM($A2)="PAID"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="101" priority="22">
+    <cfRule type="expression" dxfId="101" priority="23">
       <formula>TRIM($A2)="Finalized"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="102" priority="23">
+    <cfRule type="expression" dxfId="102" priority="24">
       <formula>TRIM($A2)="Received"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="103" priority="24">
+    <cfRule type="expression" dxfId="103" priority="25">
       <formula>TRIM($A2)="Pending"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="104" priority="25">
+    <cfRule type="expression" dxfId="104" priority="26">
       <formula>TRIM($A2)="Under Review"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="105" priority="26">
+    <cfRule type="expression" dxfId="105" priority="27">
       <formula>AND(TRIM($A2)="Denied",$K2="")</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="108" priority="29">
+    <cfRule type="expression" dxfId="108" priority="30">
       <formula>AND(TRIM($A2)="Denied",$K2&lt;&gt;"")</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="106" priority="27">
+    <cfRule type="expression" dxfId="106" priority="28">
       <formula>TRIM($A2)="Rejected"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="107" priority="28">
+    <cfRule type="expression" dxfId="107" priority="29">
       <formula>TRIM($A2)="Not found"</formula>
     </cfRule>
   </conditionalFormatting>
@@ -5878,14 +5892,15 @@
         <v>-89</v>
       </c>
       <c r="M2" s="12">
-        <f ca="1">IF($C2="","",$C2+180-TODAY())</f>
+        <f ca="1">IF(AND(TRIM($A2)="Finalized",$K2&lt;&gt;""),"",IF($C2="","",$C2+180-TODAY()))</f>
         <v>21</v>
       </c>
       <c r="N2" s="12">
-        <f ca="1">IF($C2="","",$C2+365-TODAY())</f>
+        <f ca="1">IF(AND(TRIM($A2)="Finalized",$K2&lt;&gt;""),"",IF($C2="","",$C2+365-TODAY()))</f>
         <v>206</v>
       </c>
       <c r="O2" s="6">
+        <f>IF(AND(TRIM($A2)="Finalized",$K2&lt;&gt;""),"",DATE(2026,7,8))</f>
         <v>46211</v>
       </c>
       <c r="P2" s="5" t="s">
@@ -5991,14 +6006,15 @@
         <v>-88</v>
       </c>
       <c r="M3" s="12">
-        <f ca="1">IF($C3="","",$C3+180-TODAY())</f>
+        <f ca="1">IF(AND(TRIM($A3)="Finalized",$K3&lt;&gt;""),"",IF($C3="","",$C3+180-TODAY()))</f>
         <v>21</v>
       </c>
       <c r="N3" s="12">
-        <f ca="1">IF($C3="","",$C3+365-TODAY())</f>
+        <f ca="1">IF(AND(TRIM($A3)="Finalized",$K3&lt;&gt;""),"",IF($C3="","",$C3+365-TODAY()))</f>
         <v>206</v>
       </c>
       <c r="O3" s="6">
+        <f>IF(AND(TRIM($A3)="Finalized",$K3&lt;&gt;""),"",DATE(2026,7,9))</f>
         <v>46212</v>
       </c>
       <c r="P3" s="5" t="s">
@@ -6102,14 +6118,15 @@
         <v>-85</v>
       </c>
       <c r="M4" s="12">
-        <f ca="1">IF($F4="","",$F4+90-TODAY())</f>
+        <f ca="1">IF(AND(TRIM($A4)="Finalized",$K4&lt;&gt;""),"",IF($F4="","",$F4+90-TODAY()))</f>
         <v>-85</v>
       </c>
       <c r="N4" s="12">
-        <f ca="1">IF($C4="","",$C4+365-TODAY())</f>
+        <f ca="1">IF(AND(TRIM($A4)="Finalized",$K4&lt;&gt;""),"",IF($C4="","",$C4+365-TODAY()))</f>
         <v>206</v>
       </c>
       <c r="O4" s="6">
+        <f>IF(AND(TRIM($A4)="Finalized",$K4&lt;&gt;""),"",DATE(2026,7,12))</f>
         <v>46215</v>
       </c>
       <c r="P4" s="5" t="s">
@@ -6215,14 +6232,15 @@
         <v>-82</v>
       </c>
       <c r="M5" s="12">
-        <f ca="1">IF($C5="","",$C5+180-TODAY())</f>
+        <f ca="1">IF(AND(TRIM($A5)="Finalized",$K5&lt;&gt;""),"",IF($C5="","",$C5+180-TODAY()))</f>
         <v>23</v>
       </c>
       <c r="N5" s="12">
-        <f ca="1">IF($C5="","",$C5+365-TODAY())</f>
+        <f ca="1">IF(AND(TRIM($A5)="Finalized",$K5&lt;&gt;""),"",IF($C5="","",$C5+365-TODAY()))</f>
         <v>208</v>
       </c>
       <c r="O5" s="6">
+        <f>IF(AND(TRIM($A5)="Finalized",$K5&lt;&gt;""),"",DATE(2026,7,15))</f>
         <v>46218</v>
       </c>
       <c r="P5" s="5" t="s">
@@ -6328,14 +6346,15 @@
         <v>-78</v>
       </c>
       <c r="M6" s="12">
-        <f ca="1">IF($C6="","",$C6+180-TODAY())</f>
+        <f ca="1">IF(AND(TRIM($A6)="Finalized",$K6&lt;&gt;""),"",IF($C6="","",$C6+180-TODAY()))</f>
         <v>21</v>
       </c>
       <c r="N6" s="12">
-        <f ca="1">IF($C6="","",$C6+365-TODAY())</f>
+        <f ca="1">IF(AND(TRIM($A6)="Finalized",$K6&lt;&gt;""),"",IF($C6="","",$C6+365-TODAY()))</f>
         <v>206</v>
       </c>
       <c r="O6" s="6">
+        <f>IF(AND(TRIM($A6)="Finalized",$K6&lt;&gt;""),"",DATE(2026,7,19))</f>
         <v>46222</v>
       </c>
       <c r="P6" s="5" t="s">
@@ -6441,14 +6460,15 @@
         <v>-68</v>
       </c>
       <c r="M7" s="12">
-        <f ca="1">IF($C7="","",$C7+180-TODAY())</f>
+        <f ca="1">IF(AND(TRIM($A7)="Finalized",$K7&lt;&gt;""),"",IF($C7="","",$C7+180-TODAY()))</f>
         <v>42</v>
       </c>
       <c r="N7" s="12">
-        <f ca="1">IF($C7="","",$C7+365-TODAY())</f>
+        <f ca="1">IF(AND(TRIM($A7)="Finalized",$K7&lt;&gt;""),"",IF($C7="","",$C7+365-TODAY()))</f>
         <v>227</v>
       </c>
       <c r="O7" s="6">
+        <f>IF(AND(TRIM($A7)="Finalized",$K7&lt;&gt;""),"",DATE(2026,7,29))</f>
         <v>46232</v>
       </c>
       <c r="P7" s="5" t="s">
@@ -6554,14 +6574,15 @@
         <v>-68</v>
       </c>
       <c r="M8" s="12">
-        <f ca="1">IF($F8="","",$F8+90-TODAY())</f>
+        <f ca="1">IF(AND(TRIM($A8)="Finalized",$K8&lt;&gt;""),"",IF($F8="","",$F8+90-TODAY()))</f>
         <v>-68</v>
       </c>
       <c r="N8" s="12">
-        <f ca="1">IF($C8="","",$C8+365-TODAY())</f>
+        <f ca="1">IF(AND(TRIM($A8)="Finalized",$K8&lt;&gt;""),"",IF($C8="","",$C8+365-TODAY()))</f>
         <v>227</v>
       </c>
       <c r="O8" s="6">
+        <f>IF(AND(TRIM($A8)="Finalized",$K8&lt;&gt;""),"",DATE(2026,7,29))</f>
         <v>46232</v>
       </c>
       <c r="P8" s="5" t="s">
@@ -6853,14 +6874,15 @@
         <v>179</v>
       </c>
       <c r="M11" s="12">
-        <f ca="1">IF($C11="","",$C11+365-TODAY())</f>
+        <f ca="1">IF(AND(TRIM($A11)="Finalized",$K11&lt;&gt;""),"",IF($C11="","",$C11+365-TODAY()))</f>
         <v>192</v>
       </c>
       <c r="N11" s="12">
-        <f ca="1">IF($C11="","",$C11+120-TODAY())</f>
+        <f ca="1">IF(AND(TRIM($A11)="Finalized",$K11&lt;&gt;""),"",IF($C11="","",$C11+120-TODAY()))</f>
         <v>-53</v>
       </c>
       <c r="O11" s="6">
+        <f>IF(AND(TRIM($A11)="Finalized",$K11&lt;&gt;""),"",DATE(2027,4,2))</f>
         <v>46479</v>
       </c>
       <c r="P11" s="5" t="s">
@@ -6970,14 +6992,15 @@
         <v>190</v>
       </c>
       <c r="M12" s="12">
-        <f ca="1">IF($C12="","",$C12+365-TODAY())</f>
+        <f ca="1">IF(AND(TRIM($A12)="Finalized",$K12&lt;&gt;""),"",IF($C12="","",$C12+365-TODAY()))</f>
         <v>312</v>
       </c>
       <c r="N12" s="12">
-        <f ca="1">IF($C12="","",$C12+120-TODAY())</f>
+        <f ca="1">IF(AND(TRIM($A12)="Finalized",$K12&lt;&gt;""),"",IF($C12="","",$C12+120-TODAY()))</f>
         <v>67</v>
       </c>
       <c r="O12" s="6">
+        <f>IF(AND(TRIM($A12)="Finalized",$K12&lt;&gt;""),"",DATE(2027,4,13))</f>
         <v>46490</v>
       </c>
       <c r="P12" s="5" t="s">
@@ -7083,14 +7106,15 @@
         <v>190</v>
       </c>
       <c r="M13" s="12">
-        <f ca="1">IF($C13="","",$C13+365-TODAY())</f>
+        <f ca="1">IF(AND(TRIM($A13)="Finalized",$K13&lt;&gt;""),"",IF($C13="","",$C13+365-TODAY()))</f>
         <v>216</v>
       </c>
       <c r="N13" s="12">
-        <f ca="1">IF($C13="","",$C13+120-TODAY())</f>
+        <f ca="1">IF(AND(TRIM($A13)="Finalized",$K13&lt;&gt;""),"",IF($C13="","",$C13+120-TODAY()))</f>
         <v>-29</v>
       </c>
       <c r="O13" s="6">
+        <f>IF(AND(TRIM($A13)="Finalized",$K13&lt;&gt;""),"",DATE(2027,4,13))</f>
         <v>46490</v>
       </c>
       <c r="P13" s="5" t="s">
@@ -7198,14 +7222,15 @@
         <v>197</v>
       </c>
       <c r="M14" s="12">
-        <f ca="1">IF($C14="","",$C14+365-TODAY())</f>
+        <f ca="1">IF(AND(TRIM($A14)="Finalized",$K14&lt;&gt;""),"",IF($C14="","",$C14+365-TODAY()))</f>
         <v>346</v>
       </c>
       <c r="N14" s="12">
-        <f ca="1">IF($C14="","",$C14+120-TODAY())</f>
+        <f ca="1">IF(AND(TRIM($A14)="Finalized",$K14&lt;&gt;""),"",IF($C14="","",$C14+120-TODAY()))</f>
         <v>101</v>
       </c>
       <c r="O14" s="6">
+        <f>IF(AND(TRIM($A14)="Finalized",$K14&lt;&gt;""),"",DATE(2027,4,20))</f>
         <v>46497</v>
       </c>
       <c r="P14" s="5" t="s">
@@ -7311,14 +7336,15 @@
         <v>197</v>
       </c>
       <c r="M15" s="12">
-        <f ca="1">IF($C15="","",$C15+365-TODAY())</f>
+        <f ca="1">IF(AND(TRIM($A15)="Finalized",$K15&lt;&gt;""),"",IF($C15="","",$C15+365-TODAY()))</f>
         <v>264</v>
       </c>
       <c r="N15" s="12">
-        <f ca="1">IF($C15="","",$C15+120-TODAY())</f>
+        <f ca="1">IF(AND(TRIM($A15)="Finalized",$K15&lt;&gt;""),"",IF($C15="","",$C15+120-TODAY()))</f>
         <v>19</v>
       </c>
       <c r="O15" s="6">
+        <f>IF(AND(TRIM($A15)="Finalized",$K15&lt;&gt;""),"",DATE(2027,4,20))</f>
         <v>46497</v>
       </c>
       <c r="P15" s="5" t="s">
@@ -7424,14 +7450,15 @@
         <v>204</v>
       </c>
       <c r="M16" s="12">
-        <f ca="1">IF($C16="","",$C16+365-TODAY())</f>
+        <f ca="1">IF(AND(TRIM($A16)="Finalized",$K16&lt;&gt;""),"",IF($C16="","",$C16+365-TODAY()))</f>
         <v>207</v>
       </c>
       <c r="N16" s="12">
-        <f ca="1">IF($C16="","",$C16+120-TODAY())</f>
+        <f ca="1">IF(AND(TRIM($A16)="Finalized",$K16&lt;&gt;""),"",IF($C16="","",$C16+120-TODAY()))</f>
         <v>-38</v>
       </c>
       <c r="O16" s="6">
+        <f>IF(AND(TRIM($A16)="Finalized",$K16&lt;&gt;""),"",DATE(2027,4,27))</f>
         <v>46504</v>
       </c>
       <c r="P16" s="5" t="s">
@@ -7537,14 +7564,15 @@
         <v>207</v>
       </c>
       <c r="M17" s="12">
-        <f ca="1">IF($C17="","",$C17+365-TODAY())</f>
+        <f ca="1">IF(AND(TRIM($A17)="Finalized",$K17&lt;&gt;""),"",IF($C17="","",$C17+365-TODAY()))</f>
         <v>267</v>
       </c>
       <c r="N17" s="12">
-        <f ca="1">IF($C17="","",$C17+120-TODAY())</f>
+        <f ca="1">IF(AND(TRIM($A17)="Finalized",$K17&lt;&gt;""),"",IF($C17="","",$C17+120-TODAY()))</f>
         <v>22</v>
       </c>
       <c r="O17" s="6">
+        <f>IF(AND(TRIM($A17)="Finalized",$K17&lt;&gt;""),"",DATE(2027,4,30))</f>
         <v>46507</v>
       </c>
       <c r="P17" s="5" t="s">
@@ -7654,14 +7682,15 @@
         <v>-92</v>
       </c>
       <c r="M18" s="12">
-        <f ca="1">IF($F18="","",$F18+90-TODAY())</f>
+        <f ca="1">IF(AND(TRIM($A18)="Finalized",$K18&lt;&gt;""),"",IF($F18="","",$F18+90-TODAY()))</f>
         <v>-92</v>
       </c>
       <c r="N18" s="12">
-        <f ca="1">IF($C18="","",$C18+180-TODAY())</f>
+        <f ca="1">IF(AND(TRIM($A18)="Finalized",$K18&lt;&gt;""),"",IF($C18="","",$C18+180-TODAY()))</f>
         <v>77</v>
       </c>
       <c r="O18" s="6">
+        <f>IF(AND(TRIM($A18)="Finalized",$K18&lt;&gt;""),"",DATE(2026,7,5))</f>
         <v>46208</v>
       </c>
       <c r="P18" s="5" t="s">
@@ -7767,14 +7796,15 @@
         <v>-82</v>
       </c>
       <c r="M19" s="12">
-        <f ca="1">IF($C19="","",$C19+180-TODAY())</f>
+        <f ca="1">IF(AND(TRIM($A19)="Finalized",$K19&lt;&gt;""),"",IF($C19="","",$C19+180-TODAY()))</f>
         <v>36</v>
       </c>
       <c r="N19" s="12">
-        <f ca="1">IF($C19="","",$C19+365-TODAY())</f>
+        <f ca="1">IF(AND(TRIM($A19)="Finalized",$K19&lt;&gt;""),"",IF($C19="","",$C19+365-TODAY()))</f>
         <v>221</v>
       </c>
       <c r="O19" s="6">
+        <f>IF(AND(TRIM($A19)="Finalized",$K19&lt;&gt;""),"",DATE(2026,7,15))</f>
         <v>46218</v>
       </c>
       <c r="P19" s="5" t="s">
@@ -7880,14 +7910,15 @@
         <v>-70</v>
       </c>
       <c r="M20" s="12">
-        <f ca="1">IF($F20="","",$F20+90-TODAY())</f>
+        <f ca="1">IF(AND(TRIM($A20)="Finalized",$K20&lt;&gt;""),"",IF($F20="","",$F20+90-TODAY()))</f>
         <v>-70</v>
       </c>
       <c r="N20" s="12">
-        <f ca="1">IF($C20="","",$C20+60-TODAY())</f>
+        <f ca="1">IF(AND(TRIM($A20)="Finalized",$K20&lt;&gt;""),"",IF($C20="","",$C20+60-TODAY()))</f>
         <v>-25</v>
       </c>
       <c r="O20" s="6">
+        <f>IF(AND(TRIM($A20)="Finalized",$K20&lt;&gt;""),"",DATE(2026,7,27))</f>
         <v>46230</v>
       </c>
       <c r="P20" s="5" t="s">
@@ -7995,14 +8026,15 @@
         <v>-66</v>
       </c>
       <c r="M21" s="12">
-        <f ca="1">IF($F21="","",$F21+365-TODAY())</f>
+        <f ca="1">IF(AND(TRIM($A21)="Finalized",$K21&lt;&gt;""),"",IF($F21="","",$F21+365-TODAY()))</f>
         <v>179</v>
       </c>
       <c r="N21" s="12">
-        <f ca="1">IF($C21="","",$C21+180-TODAY())</f>
+        <f ca="1">IF(AND(TRIM($A21)="Finalized",$K21&lt;&gt;""),"",IF($C21="","",$C21+180-TODAY()))</f>
         <v>34</v>
       </c>
       <c r="O21" s="6">
+        <f>IF(AND(TRIM($A21)="Finalized",$K21&lt;&gt;""),"",DATE(2026,7,31))</f>
         <v>46234</v>
       </c>
       <c r="P21" s="5" t="s">
@@ -8105,20 +8137,21 @@
       <c r="K22" s="3">
         <v>46245</v>
       </c>
-      <c r="L22" s="12">
+      <c t="str" r="L22" s="12">
         <f ca="1">IF($O22="","",$O22-TODAY())</f>
-        <v>-40</v>
-      </c>
-      <c r="M22" s="12">
-        <f ca="1">IF($C22="","",$C22+365-TODAY())</f>
-        <v>235</v>
-      </c>
-      <c r="N22" s="12">
-        <f ca="1">IF($C22="","",$C22+90-TODAY())</f>
-        <v>-40</v>
-      </c>
-      <c r="O22" s="6">
-        <v>46260</v>
+        <v/>
+      </c>
+      <c t="str" r="M22" s="12">
+        <f ca="1">IF(AND(TRIM($A22)="Finalized",$K22&lt;&gt;""),"",IF($C22="","",$C22+365-TODAY()))</f>
+        <v/>
+      </c>
+      <c t="str" r="N22" s="12">
+        <f ca="1">IF(AND(TRIM($A22)="Finalized",$K22&lt;&gt;""),"",IF($C22="","",$C22+90-TODAY()))</f>
+        <v/>
+      </c>
+      <c t="str" r="O22" s="6">
+        <f>IF(AND(TRIM($A22)="Finalized",$K22&lt;&gt;""),"",DATE(2026,8,26))</f>
+        <v/>
       </c>
       <c r="P22" s="5" t="s">
         <v>70</v>
@@ -8222,20 +8255,21 @@
       <c r="K23" s="3">
         <v>46283</v>
       </c>
-      <c r="L23" s="12">
+      <c t="str" r="L23" s="12">
         <f ca="1">IF($O23="","",$O23-TODAY())</f>
-        <v>186</v>
-      </c>
-      <c r="M23" s="12">
-        <f ca="1">IF($C23="","",$C23+365-TODAY())</f>
-        <v>314</v>
-      </c>
-      <c r="N23" s="12">
-        <f ca="1">IF($C23="","",$C23+120-TODAY())</f>
-        <v>69</v>
-      </c>
-      <c r="O23" s="6">
-        <v>46486</v>
+        <v/>
+      </c>
+      <c t="str" r="M23" s="12">
+        <f ca="1">IF(AND(TRIM($A23)="Finalized",$K23&lt;&gt;""),"",IF($C23="","",$C23+365-TODAY()))</f>
+        <v/>
+      </c>
+      <c t="str" r="N23" s="12">
+        <f ca="1">IF(AND(TRIM($A23)="Finalized",$K23&lt;&gt;""),"",IF($C23="","",$C23+120-TODAY()))</f>
+        <v/>
+      </c>
+      <c t="str" r="O23" s="6">
+        <f>IF(AND(TRIM($A23)="Finalized",$K23&lt;&gt;""),"",DATE(2027,4,9))</f>
+        <v/>
       </c>
       <c r="P23" s="5" t="s">
         <v>67</v>
@@ -8333,20 +8367,21 @@
       <c r="K24" s="3">
         <v>46283</v>
       </c>
-      <c r="L24" s="12">
+      <c t="str" r="L24" s="12">
         <f ca="1">IF($O24="","",$O24-TODAY())</f>
-        <v>190</v>
-      </c>
-      <c r="M24" s="12">
-        <f ca="1">IF($C24="","",$C24+365-TODAY())</f>
-        <v>204</v>
-      </c>
-      <c r="N24" s="12">
-        <f ca="1">IF($C24="","",$C24+120-TODAY())</f>
-        <v>-41</v>
-      </c>
-      <c r="O24" s="6">
-        <v>46490</v>
+        <v/>
+      </c>
+      <c t="str" r="M24" s="12">
+        <f ca="1">IF(AND(TRIM($A24)="Finalized",$K24&lt;&gt;""),"",IF($C24="","",$C24+365-TODAY()))</f>
+        <v/>
+      </c>
+      <c t="str" r="N24" s="12">
+        <f ca="1">IF(AND(TRIM($A24)="Finalized",$K24&lt;&gt;""),"",IF($C24="","",$C24+120-TODAY()))</f>
+        <v/>
+      </c>
+      <c t="str" r="O24" s="6">
+        <f>IF(AND(TRIM($A24)="Finalized",$K24&lt;&gt;""),"",DATE(2027,4,13))</f>
+        <v/>
       </c>
       <c r="P24" s="5" t="s">
         <v>67</v>
@@ -8446,20 +8481,21 @@
       <c r="K25" s="3">
         <v>46300</v>
       </c>
-      <c r="L25" s="12">
+      <c t="str" r="L25" s="12">
         <f ca="1">IF($O25="","",$O25-TODAY())</f>
-        <v>191</v>
-      </c>
-      <c r="M25" s="12">
-        <f ca="1">IF($C25="","",$C25+365-TODAY())</f>
-        <v>213</v>
-      </c>
-      <c r="N25" s="12">
-        <f ca="1">IF($C25="","",$C25+120-TODAY())</f>
-        <v>-32</v>
-      </c>
-      <c r="O25" s="6">
-        <v>46491</v>
+        <v/>
+      </c>
+      <c t="str" r="M25" s="12">
+        <f ca="1">IF(AND(TRIM($A25)="Finalized",$K25&lt;&gt;""),"",IF($C25="","",$C25+365-TODAY()))</f>
+        <v/>
+      </c>
+      <c t="str" r="N25" s="12">
+        <f ca="1">IF(AND(TRIM($A25)="Finalized",$K25&lt;&gt;""),"",IF($C25="","",$C25+120-TODAY()))</f>
+        <v/>
+      </c>
+      <c t="str" r="O25" s="6">
+        <f>IF(AND(TRIM($A25)="Finalized",$K25&lt;&gt;""),"",DATE(2027,4,14))</f>
+        <v/>
       </c>
       <c r="P25" s="5" t="s">
         <v>67</v>
@@ -8559,20 +8595,21 @@
       <c r="K26" s="3">
         <v>46284</v>
       </c>
-      <c r="L26" s="12">
+      <c t="str" r="L26" s="12">
         <f ca="1">IF($O26="","",$O26-TODAY())</f>
-        <v>-92</v>
-      </c>
-      <c r="M26" s="12">
-        <f ca="1">IF($C26="","",$C26+180-TODAY())</f>
-        <v>7</v>
-      </c>
-      <c r="N26" s="12">
-        <f ca="1">IF($C26="","",$C26+365-TODAY())</f>
-        <v>192</v>
-      </c>
-      <c r="O26" s="6">
-        <v>46208</v>
+        <v/>
+      </c>
+      <c t="str" r="M26" s="12">
+        <f ca="1">IF(AND(TRIM($A26)="Finalized",$K26&lt;&gt;""),"",IF($C26="","",$C26+180-TODAY()))</f>
+        <v/>
+      </c>
+      <c t="str" r="N26" s="12">
+        <f ca="1">IF(AND(TRIM($A26)="Finalized",$K26&lt;&gt;""),"",IF($C26="","",$C26+365-TODAY()))</f>
+        <v/>
+      </c>
+      <c t="str" r="O26" s="6">
+        <f>IF(AND(TRIM($A26)="Finalized",$K26&lt;&gt;""),"",DATE(2026,7,5))</f>
+        <v/>
       </c>
       <c r="P26" s="5" t="s">
         <v>87</v>
@@ -8672,20 +8709,21 @@
       <c r="K27" s="3">
         <v>46285</v>
       </c>
-      <c r="L27" s="12">
+      <c t="str" r="L27" s="12">
         <f ca="1">IF($O27="","",$O27-TODAY())</f>
-        <v>-85</v>
-      </c>
-      <c r="M27" s="12">
-        <f ca="1">IF($C27="","",$C27+365-TODAY())</f>
-        <v>235</v>
-      </c>
-      <c r="N27" s="12">
-        <f ca="1">IF($C27="","",$C27+365-TODAY())</f>
-        <v>235</v>
-      </c>
-      <c r="O27" s="6">
-        <v>46215</v>
+        <v/>
+      </c>
+      <c t="str" r="M27" s="12">
+        <f ca="1">IF(AND(TRIM($A27)="Finalized",$K27&lt;&gt;""),"",IF($C27="","",$C27+365-TODAY()))</f>
+        <v/>
+      </c>
+      <c t="str" r="N27" s="12">
+        <f ca="1">IF(AND(TRIM($A27)="Finalized",$K27&lt;&gt;""),"",IF($C27="","",$C27+365-TODAY()))</f>
+        <v/>
+      </c>
+      <c t="str" r="O27" s="6">
+        <f>IF(AND(TRIM($A27)="Finalized",$K27&lt;&gt;""),"",DATE(2026,7,12))</f>
+        <v/>
       </c>
       <c r="P27" s="5" t="s">
         <v>87</v>
@@ -8787,20 +8825,21 @@
       <c r="K28" s="3">
         <v>46285</v>
       </c>
-      <c r="L28" s="12">
+      <c t="str" r="L28" s="12">
         <f ca="1">IF($O28="","",$O28-TODAY())</f>
-        <v>-85</v>
-      </c>
-      <c r="M28" s="12">
-        <f ca="1">IF($C28="","",$C28+365-TODAY())</f>
-        <v>232</v>
-      </c>
-      <c r="N28" s="12">
-        <f ca="1">IF($C28="","",$C28+365-TODAY())</f>
-        <v>232</v>
-      </c>
-      <c r="O28" s="6">
-        <v>46215</v>
+        <v/>
+      </c>
+      <c t="str" r="M28" s="12">
+        <f ca="1">IF(AND(TRIM($A28)="Finalized",$K28&lt;&gt;""),"",IF($C28="","",$C28+365-TODAY()))</f>
+        <v/>
+      </c>
+      <c t="str" r="N28" s="12">
+        <f ca="1">IF(AND(TRIM($A28)="Finalized",$K28&lt;&gt;""),"",IF($C28="","",$C28+365-TODAY()))</f>
+        <v/>
+      </c>
+      <c t="str" r="O28" s="6">
+        <f>IF(AND(TRIM($A28)="Finalized",$K28&lt;&gt;""),"",DATE(2026,7,12))</f>
+        <v/>
       </c>
       <c r="P28" s="5" t="s">
         <v>87</v>
@@ -8902,20 +8941,21 @@
       <c r="K29" s="3">
         <v>46285</v>
       </c>
-      <c r="L29" s="12">
+      <c t="str" r="L29" s="12">
         <f ca="1">IF($O29="","",$O29-TODAY())</f>
-        <v>-82</v>
-      </c>
-      <c r="M29" s="12">
-        <f ca="1">IF($C29="","",$C29+365-TODAY())</f>
-        <v>235</v>
-      </c>
-      <c r="N29" s="12">
-        <f ca="1">IF($C29="","",$C29+365-TODAY())</f>
-        <v>235</v>
-      </c>
-      <c r="O29" s="6">
-        <v>46218</v>
+        <v/>
+      </c>
+      <c t="str" r="M29" s="12">
+        <f ca="1">IF(AND(TRIM($A29)="Finalized",$K29&lt;&gt;""),"",IF($C29="","",$C29+365-TODAY()))</f>
+        <v/>
+      </c>
+      <c t="str" r="N29" s="12">
+        <f ca="1">IF(AND(TRIM($A29)="Finalized",$K29&lt;&gt;""),"",IF($C29="","",$C29+365-TODAY()))</f>
+        <v/>
+      </c>
+      <c t="str" r="O29" s="6">
+        <f>IF(AND(TRIM($A29)="Finalized",$K29&lt;&gt;""),"",DATE(2026,7,15))</f>
+        <v/>
       </c>
       <c r="P29" s="5" t="s">
         <v>87</v>
@@ -9017,20 +9057,21 @@
       <c r="K30" s="3">
         <v>46285</v>
       </c>
-      <c r="L30" s="12">
+      <c t="str" r="L30" s="12">
         <f ca="1">IF($O30="","",$O30-TODAY())</f>
-        <v>-75</v>
-      </c>
-      <c r="M30" s="12">
-        <f ca="1">IF($C30="","",$C30+180-TODAY())</f>
-        <v>34</v>
-      </c>
-      <c r="N30" s="12">
-        <f ca="1">IF($C30="","",$C30+365-TODAY())</f>
-        <v>219</v>
-      </c>
-      <c r="O30" s="6">
-        <v>46225</v>
+        <v/>
+      </c>
+      <c t="str" r="M30" s="12">
+        <f ca="1">IF(AND(TRIM($A30)="Finalized",$K30&lt;&gt;""),"",IF($C30="","",$C30+180-TODAY()))</f>
+        <v/>
+      </c>
+      <c t="str" r="N30" s="12">
+        <f ca="1">IF(AND(TRIM($A30)="Finalized",$K30&lt;&gt;""),"",IF($C30="","",$C30+365-TODAY()))</f>
+        <v/>
+      </c>
+      <c t="str" r="O30" s="6">
+        <f>IF(AND(TRIM($A30)="Finalized",$K30&lt;&gt;""),"",DATE(2026,7,22))</f>
+        <v/>
       </c>
       <c r="P30" s="5" t="s">
         <v>87</v>
@@ -9128,20 +9169,21 @@
       <c r="K31" s="3">
         <v>46285</v>
       </c>
-      <c r="L31" s="12">
+      <c t="str" r="L31" s="12">
         <f ca="1">IF($O31="","",$O31-TODAY())</f>
-        <v>-71</v>
-      </c>
-      <c r="M31" s="12">
-        <f ca="1">IF($C31="","",$C31+180-TODAY())</f>
-        <v>36</v>
-      </c>
-      <c r="N31" s="12">
-        <f ca="1">IF($C31="","",$C31+365-TODAY())</f>
-        <v>221</v>
-      </c>
-      <c r="O31" s="6">
-        <v>46229</v>
+        <v/>
+      </c>
+      <c t="str" r="M31" s="12">
+        <f ca="1">IF(AND(TRIM($A31)="Finalized",$K31&lt;&gt;""),"",IF($C31="","",$C31+180-TODAY()))</f>
+        <v/>
+      </c>
+      <c t="str" r="N31" s="12">
+        <f ca="1">IF(AND(TRIM($A31)="Finalized",$K31&lt;&gt;""),"",IF($C31="","",$C31+365-TODAY()))</f>
+        <v/>
+      </c>
+      <c t="str" r="O31" s="6">
+        <f>IF(AND(TRIM($A31)="Finalized",$K31&lt;&gt;""),"",DATE(2026,7,26))</f>
+        <v/>
       </c>
       <c r="P31" s="5" t="s">
         <v>87</v>
@@ -9243,20 +9285,21 @@
       <c r="K32" s="3">
         <v>46285</v>
       </c>
-      <c r="L32" s="12">
+      <c t="str" r="L32" s="12">
         <f ca="1">IF($O32="","",$O32-TODAY())</f>
-        <v>-71</v>
-      </c>
-      <c r="M32" s="12">
-        <f ca="1">IF($C32="","",$C32+365-TODAY())</f>
-        <v>282</v>
-      </c>
-      <c r="N32" s="12">
-        <f ca="1">IF($C32="","",$C32+365-TODAY())</f>
-        <v>282</v>
-      </c>
-      <c r="O32" s="6">
-        <v>46229</v>
+        <v/>
+      </c>
+      <c t="str" r="M32" s="12">
+        <f ca="1">IF(AND(TRIM($A32)="Finalized",$K32&lt;&gt;""),"",IF($C32="","",$C32+365-TODAY()))</f>
+        <v/>
+      </c>
+      <c t="str" r="N32" s="12">
+        <f ca="1">IF(AND(TRIM($A32)="Finalized",$K32&lt;&gt;""),"",IF($C32="","",$C32+365-TODAY()))</f>
+        <v/>
+      </c>
+      <c t="str" r="O32" s="6">
+        <f>IF(AND(TRIM($A32)="Finalized",$K32&lt;&gt;""),"",DATE(2026,7,26))</f>
+        <v/>
       </c>
       <c r="P32" s="5" t="s">
         <v>87</v>
@@ -9326,100 +9369,105 @@
     </row>
   </sheetData>
   <autoFilter ref="A1:AN32" xr:uid="{00000000-0009-0000-0000-000001000000}"/>
+  <conditionalFormatting sqref="L2:O1000">
+    <cfRule type="expression" dxfId="101" priority="1" stopIfTrue="1">
+      <formula>AND(TRIM($A2)="Finalized",$K2&lt;&gt;"")</formula>
+    </cfRule>
+  </conditionalFormatting>
   <conditionalFormatting sqref="L2:L32">
-    <cfRule type="expression" dxfId="79" priority="1">
+    <cfRule type="expression" dxfId="79" priority="2">
       <formula>AND($L2&lt;&gt;"", $L2&gt;=0, $L2&lt;=5)</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="78" priority="2">
+    <cfRule type="expression" dxfId="78" priority="3">
       <formula>AND($L2&lt;&gt;"", $L2&gt;5, $L2&lt;=30)</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="77" priority="3">
+    <cfRule type="expression" dxfId="77" priority="4">
       <formula>AND($L2&lt;&gt;"", $L2&gt;30)</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="76" priority="4">
+    <cfRule type="expression" dxfId="76" priority="5">
       <formula>AND($L2&lt;&gt;"", $L2&lt;0)</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="75" priority="5">
+    <cfRule type="expression" dxfId="75" priority="6">
       <formula>$L2=""</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="M2:M32">
-    <cfRule type="expression" dxfId="74" priority="6">
+    <cfRule type="expression" dxfId="74" priority="7">
       <formula>AND($M2&lt;&gt;"", $M2&gt;=0, $M2&lt;=5)</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="73" priority="7">
+    <cfRule type="expression" dxfId="73" priority="8">
       <formula>AND($M2&lt;&gt;"", $M2&gt;5, $M2&lt;=30)</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="72" priority="8">
+    <cfRule type="expression" dxfId="72" priority="9">
       <formula>AND($M2&lt;&gt;"", $M2&gt;30)</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="71" priority="9">
+    <cfRule type="expression" dxfId="71" priority="10">
       <formula>AND($M2&lt;&gt;"", $M2&lt;0)</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="70" priority="10">
+    <cfRule type="expression" dxfId="70" priority="11">
       <formula>$M2=""</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="N2:N32">
-    <cfRule type="expression" dxfId="69" priority="11">
+    <cfRule type="expression" dxfId="69" priority="12">
       <formula>AND($N2&lt;&gt;"", $N2&gt;=0, $N2&lt;=5)</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="68" priority="12">
+    <cfRule type="expression" dxfId="68" priority="13">
       <formula>AND($N2&lt;&gt;"", $N2&gt;5, $N2&lt;=30)</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="67" priority="13">
+    <cfRule type="expression" dxfId="67" priority="14">
       <formula>AND($N2&lt;&gt;"", $N2&gt;30)</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="66" priority="14">
+    <cfRule type="expression" dxfId="66" priority="15">
       <formula>AND($N2&lt;&gt;"", $N2&lt;0)</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="65" priority="15">
+    <cfRule type="expression" dxfId="65" priority="16">
       <formula>$N2=""</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="O2:U32">
-    <cfRule type="expression" dxfId="64" priority="16">
+    <cfRule type="expression" dxfId="64" priority="17">
       <formula>AND($L2&lt;&gt;"", $L2&gt;=0, $L2&lt;=5)</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="63" priority="17">
+    <cfRule type="expression" dxfId="63" priority="18">
       <formula>AND($L2&lt;&gt;"", $L2&gt;5, $L2&lt;=30)</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="62" priority="18">
+    <cfRule type="expression" dxfId="62" priority="19">
       <formula>AND($L2&lt;&gt;"", $L2&gt;30)</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="61" priority="19">
+    <cfRule type="expression" dxfId="61" priority="20">
       <formula>AND($L2&lt;&gt;"", $L2&lt;0)</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="60" priority="20">
+    <cfRule type="expression" dxfId="60" priority="21">
       <formula>$L2=""</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A2:AN1000">
-    <cfRule type="expression" dxfId="100" priority="21">
+    <cfRule type="expression" dxfId="100" priority="22">
       <formula>TRIM($A2)="PAID"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="101" priority="22">
+    <cfRule type="expression" dxfId="101" priority="23">
       <formula>TRIM($A2)="Finalized"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="102" priority="23">
+    <cfRule type="expression" dxfId="102" priority="24">
       <formula>TRIM($A2)="Received"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="103" priority="24">
+    <cfRule type="expression" dxfId="103" priority="25">
       <formula>TRIM($A2)="Pending"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="104" priority="25">
+    <cfRule type="expression" dxfId="104" priority="26">
       <formula>TRIM($A2)="Under Review"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="105" priority="26">
+    <cfRule type="expression" dxfId="105" priority="27">
       <formula>AND(TRIM($A2)="Denied",$K2="")</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="108" priority="29">
+    <cfRule type="expression" dxfId="108" priority="30">
       <formula>AND(TRIM($A2)="Denied",$K2&lt;&gt;"")</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="106" priority="27">
+    <cfRule type="expression" dxfId="106" priority="28">
       <formula>TRIM($A2)="Rejected"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="107" priority="28">
+    <cfRule type="expression" dxfId="107" priority="29">
       <formula>TRIM($A2)="Not found"</formula>
     </cfRule>
   </conditionalFormatting>
@@ -9635,14 +9683,15 @@
         <v>-92</v>
       </c>
       <c r="M2" s="12">
-        <f ca="1">IF($F2="","",$F2+90-TODAY())</f>
+        <f ca="1">IF(AND(TRIM($A2)="Finalized",$K2&lt;&gt;""),"",IF($F2="","",$F2+90-TODAY()))</f>
         <v>-92</v>
       </c>
       <c r="N2" s="12">
-        <f ca="1">IF($C2="","",$C2+540-TODAY())</f>
+        <f ca="1">IF(AND(TRIM($A2)="Finalized",$K2&lt;&gt;""),"",IF($C2="","",$C2+540-TODAY()))</f>
         <v>405</v>
       </c>
       <c r="O2" s="6">
+        <f>IF(AND(TRIM($A2)="Finalized",$K2&lt;&gt;""),"",DATE(2026,7,5))</f>
         <v>46208</v>
       </c>
       <c r="P2" s="5" t="s">
@@ -9754,14 +9803,15 @@
         <v>-85</v>
       </c>
       <c r="M3" s="12">
-        <f ca="1">IF($F3="","",$F3+90-TODAY())</f>
+        <f ca="1">IF(AND(TRIM($A3)="Finalized",$K3&lt;&gt;""),"",IF($F3="","",$F3+90-TODAY()))</f>
         <v>-85</v>
       </c>
       <c r="N3" s="12">
-        <f ca="1">IF($C3="","",$C3+180-TODAY())</f>
+        <f ca="1">IF(AND(TRIM($A3)="Finalized",$K3&lt;&gt;""),"",IF($C3="","",$C3+180-TODAY()))</f>
         <v>42</v>
       </c>
       <c r="O3" s="6">
+        <f>IF(AND(TRIM($A3)="Finalized",$K3&lt;&gt;""),"",DATE(2026,7,12))</f>
         <v>46215</v>
       </c>
       <c r="P3" s="5" t="s">
@@ -9873,14 +9923,15 @@
         <v>190</v>
       </c>
       <c r="M4" s="12">
-        <f ca="1">IF($C4="","",$C4+180-TODAY())</f>
+        <f ca="1">IF(AND(TRIM($A4)="Finalized",$K4&lt;&gt;""),"",IF($C4="","",$C4+180-TODAY()))</f>
         <v>70</v>
       </c>
       <c r="N4" s="12">
-        <f ca="1">IF($C4="","",$C4+365-TODAY())</f>
+        <f ca="1">IF(AND(TRIM($A4)="Finalized",$K4&lt;&gt;""),"",IF($C4="","",$C4+365-TODAY()))</f>
         <v>255</v>
       </c>
       <c r="O4" s="6">
+        <f>IF(AND(TRIM($A4)="Finalized",$K4&lt;&gt;""),"",DATE(2027,4,13))</f>
         <v>46490</v>
       </c>
       <c r="P4" s="5" t="s">
@@ -9994,14 +10045,15 @@
         <v>-78</v>
       </c>
       <c r="M5" s="12">
-        <f ca="1">IF($F5="","",$F5+90-TODAY())</f>
+        <f ca="1">IF(AND(TRIM($A5)="Finalized",$K5&lt;&gt;""),"",IF($F5="","",$F5+90-TODAY()))</f>
         <v>-78</v>
       </c>
       <c r="N5" s="12">
-        <f ca="1">IF($C5="","",$C5+365-TODAY())</f>
+        <f ca="1">IF(AND(TRIM($A5)="Finalized",$K5&lt;&gt;""),"",IF($C5="","",$C5+365-TODAY()))</f>
         <v>227</v>
       </c>
       <c r="O5" s="6">
+        <f>IF(AND(TRIM($A5)="Finalized",$K5&lt;&gt;""),"",DATE(2026,7,19))</f>
         <v>46222</v>
       </c>
       <c r="P5" s="5" t="s">
@@ -10112,20 +10164,21 @@
       <c r="K6" s="3">
         <v>46278</v>
       </c>
-      <c r="L6" s="12">
+      <c t="str" r="L6" s="12">
         <f ca="1">IF($O6="","",$O6-TODAY())</f>
-        <v>12</v>
-      </c>
-      <c r="M6" s="12">
-        <f ca="1">IF($F6="","",$F6+365-TODAY())</f>
-        <v>197</v>
-      </c>
-      <c r="N6" s="12">
-        <f ca="1">IF($F6="","",$F6+365-TODAY())</f>
-        <v>197</v>
-      </c>
-      <c r="O6" s="6">
-        <v>46312</v>
+        <v/>
+      </c>
+      <c t="str" r="M6" s="12">
+        <f ca="1">IF(AND(TRIM($A6)="Finalized",$K6&lt;&gt;""),"",IF($F6="","",$F6+365-TODAY()))</f>
+        <v/>
+      </c>
+      <c t="str" r="N6" s="12">
+        <f ca="1">IF(AND(TRIM($A6)="Finalized",$K6&lt;&gt;""),"",IF($F6="","",$F6+365-TODAY()))</f>
+        <v/>
+      </c>
+      <c t="str" r="O6" s="6">
+        <f>IF(AND(TRIM($A6)="Finalized",$K6&lt;&gt;""),"",DATE(2026,10,17))</f>
+        <v/>
       </c>
       <c r="P6" s="5" t="s">
         <v>179</v>
@@ -10304,100 +10357,105 @@
     </row>
   </sheetData>
   <autoFilter ref="A1:AN7" xr:uid="{00000000-0009-0000-0000-000002000000}"/>
+  <conditionalFormatting sqref="L2:O1000">
+    <cfRule type="expression" dxfId="101" priority="1" stopIfTrue="1">
+      <formula>AND(TRIM($A2)="Finalized",$K2&lt;&gt;"")</formula>
+    </cfRule>
+  </conditionalFormatting>
   <conditionalFormatting sqref="L2:L7">
-    <cfRule type="expression" dxfId="59" priority="1">
+    <cfRule type="expression" dxfId="59" priority="2">
       <formula>AND($L2&lt;&gt;"", $L2&gt;=0, $L2&lt;=5)</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="58" priority="2">
+    <cfRule type="expression" dxfId="58" priority="3">
       <formula>AND($L2&lt;&gt;"", $L2&gt;5, $L2&lt;=30)</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="57" priority="3">
+    <cfRule type="expression" dxfId="57" priority="4">
       <formula>AND($L2&lt;&gt;"", $L2&gt;30)</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="56" priority="4">
+    <cfRule type="expression" dxfId="56" priority="5">
       <formula>AND($L2&lt;&gt;"", $L2&lt;0)</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="55" priority="5">
+    <cfRule type="expression" dxfId="55" priority="6">
       <formula>$L2=""</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="M2:M7">
-    <cfRule type="expression" dxfId="54" priority="6">
+    <cfRule type="expression" dxfId="54" priority="7">
       <formula>AND($M2&lt;&gt;"", $M2&gt;=0, $M2&lt;=5)</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="53" priority="7">
+    <cfRule type="expression" dxfId="53" priority="8">
       <formula>AND($M2&lt;&gt;"", $M2&gt;5, $M2&lt;=30)</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="52" priority="8">
+    <cfRule type="expression" dxfId="52" priority="9">
       <formula>AND($M2&lt;&gt;"", $M2&gt;30)</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="51" priority="9">
+    <cfRule type="expression" dxfId="51" priority="10">
       <formula>AND($M2&lt;&gt;"", $M2&lt;0)</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="50" priority="10">
+    <cfRule type="expression" dxfId="50" priority="11">
       <formula>$M2=""</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="N2:N7">
-    <cfRule type="expression" dxfId="49" priority="11">
+    <cfRule type="expression" dxfId="49" priority="12">
       <formula>AND($N2&lt;&gt;"", $N2&gt;=0, $N2&lt;=5)</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="48" priority="12">
+    <cfRule type="expression" dxfId="48" priority="13">
       <formula>AND($N2&lt;&gt;"", $N2&gt;5, $N2&lt;=30)</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="47" priority="13">
+    <cfRule type="expression" dxfId="47" priority="14">
       <formula>AND($N2&lt;&gt;"", $N2&gt;30)</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="46" priority="14">
+    <cfRule type="expression" dxfId="46" priority="15">
       <formula>AND($N2&lt;&gt;"", $N2&lt;0)</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="45" priority="15">
+    <cfRule type="expression" dxfId="45" priority="16">
       <formula>$N2=""</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="O2:U7">
-    <cfRule type="expression" dxfId="44" priority="16">
+    <cfRule type="expression" dxfId="44" priority="17">
       <formula>AND($L2&lt;&gt;"", $L2&gt;=0, $L2&lt;=5)</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="43" priority="17">
+    <cfRule type="expression" dxfId="43" priority="18">
       <formula>AND($L2&lt;&gt;"", $L2&gt;5, $L2&lt;=30)</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="42" priority="18">
+    <cfRule type="expression" dxfId="42" priority="19">
       <formula>AND($L2&lt;&gt;"", $L2&gt;30)</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="41" priority="19">
+    <cfRule type="expression" dxfId="41" priority="20">
       <formula>AND($L2&lt;&gt;"", $L2&lt;0)</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="40" priority="20">
+    <cfRule type="expression" dxfId="40" priority="21">
       <formula>$L2=""</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A2:AN1000">
-    <cfRule type="expression" dxfId="100" priority="21">
+    <cfRule type="expression" dxfId="100" priority="22">
       <formula>TRIM($A2)="PAID"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="101" priority="22">
+    <cfRule type="expression" dxfId="101" priority="23">
       <formula>TRIM($A2)="Finalized"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="102" priority="23">
+    <cfRule type="expression" dxfId="102" priority="24">
       <formula>TRIM($A2)="Received"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="103" priority="24">
+    <cfRule type="expression" dxfId="103" priority="25">
       <formula>TRIM($A2)="Pending"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="104" priority="25">
+    <cfRule type="expression" dxfId="104" priority="26">
       <formula>TRIM($A2)="Under Review"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="105" priority="26">
+    <cfRule type="expression" dxfId="105" priority="27">
       <formula>AND(TRIM($A2)="Denied",$K2="")</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="108" priority="29">
+    <cfRule type="expression" dxfId="108" priority="30">
       <formula>AND(TRIM($A2)="Denied",$K2&lt;&gt;"")</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="106" priority="27">
+    <cfRule type="expression" dxfId="106" priority="28">
       <formula>TRIM($A2)="Rejected"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="107" priority="28">
+    <cfRule type="expression" dxfId="107" priority="29">
       <formula>TRIM($A2)="Not found"</formula>
     </cfRule>
   </conditionalFormatting>
@@ -10802,14 +10860,15 @@
         <v>183</v>
       </c>
       <c r="M4" s="12">
-        <f ca="1">IF($C4="","",$C4+365-TODAY())</f>
+        <f ca="1">IF(AND(TRIM($A4)="Finalized",$K4&lt;&gt;""),"",IF($C4="","",$C4+365-TODAY()))</f>
         <v>200</v>
       </c>
       <c r="N4" s="12">
-        <f ca="1">IF($C4="","",$C4+120-TODAY())</f>
+        <f ca="1">IF(AND(TRIM($A4)="Finalized",$K4&lt;&gt;""),"",IF($C4="","",$C4+120-TODAY()))</f>
         <v>-45</v>
       </c>
       <c r="O4" s="6">
+        <f>IF(AND(TRIM($A4)="Finalized",$K4&lt;&gt;""),"",DATE(2027,4,6))</f>
         <v>46483</v>
       </c>
       <c r="P4" s="5" t="s">
@@ -10915,14 +10974,15 @@
         <v>183</v>
       </c>
       <c r="M5" s="12">
-        <f ca="1">IF($C5="","",$C5+365-TODAY())</f>
+        <f ca="1">IF(AND(TRIM($A5)="Finalized",$K5&lt;&gt;""),"",IF($C5="","",$C5+365-TODAY()))</f>
         <v>205</v>
       </c>
       <c r="N5" s="12">
-        <f ca="1">IF($C5="","",$C5+120-TODAY())</f>
+        <f ca="1">IF(AND(TRIM($A5)="Finalized",$K5&lt;&gt;""),"",IF($C5="","",$C5+120-TODAY()))</f>
         <v>-40</v>
       </c>
       <c r="O5" s="6">
+        <f>IF(AND(TRIM($A5)="Finalized",$K5&lt;&gt;""),"",DATE(2027,4,6))</f>
         <v>46483</v>
       </c>
       <c r="P5" s="5" t="s">
@@ -11028,14 +11088,15 @@
         <v>193</v>
       </c>
       <c r="M6" s="12">
-        <f ca="1">IF($C6="","",$C6+365-TODAY())</f>
+        <f ca="1">IF(AND(TRIM($A6)="Finalized",$K6&lt;&gt;""),"",IF($C6="","",$C6+365-TODAY()))</f>
         <v>201</v>
       </c>
       <c r="N6" s="12">
-        <f ca="1">IF($C6="","",$C6+120-TODAY())</f>
+        <f ca="1">IF(AND(TRIM($A6)="Finalized",$K6&lt;&gt;""),"",IF($C6="","",$C6+120-TODAY()))</f>
         <v>-44</v>
       </c>
       <c r="O6" s="6">
+        <f>IF(AND(TRIM($A6)="Finalized",$K6&lt;&gt;""),"",DATE(2027,4,16))</f>
         <v>46493</v>
       </c>
       <c r="P6" s="5" t="s">
@@ -11139,14 +11200,15 @@
         <v>197</v>
       </c>
       <c r="M7" s="12">
-        <f ca="1">IF($C7="","",$C7+365-TODAY())</f>
+        <f ca="1">IF(AND(TRIM($A7)="Finalized",$K7&lt;&gt;""),"",IF($C7="","",$C7+365-TODAY()))</f>
         <v>201</v>
       </c>
       <c r="N7" s="12">
-        <f ca="1">IF($C7="","",$C7+120-TODAY())</f>
+        <f ca="1">IF(AND(TRIM($A7)="Finalized",$K7&lt;&gt;""),"",IF($C7="","",$C7+120-TODAY()))</f>
         <v>-44</v>
       </c>
       <c r="O7" s="6">
+        <f>IF(AND(TRIM($A7)="Finalized",$K7&lt;&gt;""),"",DATE(2027,4,20))</f>
         <v>46497</v>
       </c>
       <c r="P7" s="5" t="s">
@@ -11252,14 +11314,15 @@
         <v>200</v>
       </c>
       <c r="M8" s="12">
-        <f ca="1">IF($C8="","",$C8+365-TODAY())</f>
+        <f ca="1">IF(AND(TRIM($A8)="Finalized",$K8&lt;&gt;""),"",IF($C8="","",$C8+365-TODAY()))</f>
         <v>212</v>
       </c>
       <c r="N8" s="12">
-        <f ca="1">IF($C8="","",$C8+120-TODAY())</f>
+        <f ca="1">IF(AND(TRIM($A8)="Finalized",$K8&lt;&gt;""),"",IF($C8="","",$C8+120-TODAY()))</f>
         <v>-33</v>
       </c>
       <c r="O8" s="6">
+        <f>IF(AND(TRIM($A8)="Finalized",$K8&lt;&gt;""),"",DATE(2027,4,23))</f>
         <v>46500</v>
       </c>
       <c r="P8" s="5" t="s">
@@ -11367,14 +11430,15 @@
         <v>-97</v>
       </c>
       <c r="M9" s="12">
-        <f ca="1">IF($C9="","",$C9+180-TODAY())</f>
+        <f ca="1">IF(AND(TRIM($A9)="Finalized",$K9&lt;&gt;""),"",IF($C9="","",$C9+180-TODAY()))</f>
         <v>98</v>
       </c>
       <c r="N9" s="12">
-        <f ca="1">IF($C9="","",$C9+365-TODAY())</f>
+        <f ca="1">IF(AND(TRIM($A9)="Finalized",$K9&lt;&gt;""),"",IF($C9="","",$C9+365-TODAY()))</f>
         <v>283</v>
       </c>
       <c r="O9" s="6">
+        <f>IF(AND(TRIM($A9)="Finalized",$K9&lt;&gt;""),"",DATE(2026,6,30))</f>
         <v>46203</v>
       </c>
       <c r="P9" s="5" t="s">
@@ -11482,14 +11546,15 @@
         <v>-83</v>
       </c>
       <c r="M10" s="12">
-        <f ca="1">IF($C10="","",$C10+180-TODAY())</f>
+        <f ca="1">IF(AND(TRIM($A10)="Finalized",$K10&lt;&gt;""),"",IF($C10="","",$C10+180-TODAY()))</f>
         <v>132</v>
       </c>
       <c r="N10" s="12">
-        <f ca="1">IF($C10="","",$C10+365-TODAY())</f>
+        <f ca="1">IF(AND(TRIM($A10)="Finalized",$K10&lt;&gt;""),"",IF($C10="","",$C10+365-TODAY()))</f>
         <v>317</v>
       </c>
       <c r="O10" s="6">
+        <f>IF(AND(TRIM($A10)="Finalized",$K10&lt;&gt;""),"",DATE(2026,7,14))</f>
         <v>46217</v>
       </c>
       <c r="P10" s="5" t="s">
@@ -11597,14 +11662,15 @@
         <v>-75</v>
       </c>
       <c r="M11" s="12">
-        <f ca="1">IF($F11="","",$F11+90-TODAY())</f>
+        <f ca="1">IF(AND(TRIM($A11)="Finalized",$K11&lt;&gt;""),"",IF($F11="","",$F11+90-TODAY()))</f>
         <v>-75</v>
       </c>
       <c r="N11" s="12">
-        <f ca="1">IF($C11="","",$C11+60-TODAY())</f>
+        <f ca="1">IF(AND(TRIM($A11)="Finalized",$K11&lt;&gt;""),"",IF($C11="","",$C11+60-TODAY()))</f>
         <v>-38</v>
       </c>
       <c r="O11" s="6">
+        <f>IF(AND(TRIM($A11)="Finalized",$K11&lt;&gt;""),"",DATE(2026,7,22))</f>
         <v>46225</v>
       </c>
       <c r="P11" s="5" t="s">
@@ -11712,14 +11778,15 @@
         <v>-71</v>
       </c>
       <c r="M12" s="12">
-        <f ca="1">IF($C12="","",$C12+180-TODAY())</f>
+        <f ca="1">IF(AND(TRIM($A12)="Finalized",$K12&lt;&gt;""),"",IF($C12="","",$C12+180-TODAY()))</f>
         <v>36</v>
       </c>
       <c r="N12" s="12">
-        <f ca="1">IF($C12="","",$C12+365-TODAY())</f>
+        <f ca="1">IF(AND(TRIM($A12)="Finalized",$K12&lt;&gt;""),"",IF($C12="","",$C12+365-TODAY()))</f>
         <v>221</v>
       </c>
       <c r="O12" s="6">
+        <f>IF(AND(TRIM($A12)="Finalized",$K12&lt;&gt;""),"",DATE(2026,7,26))</f>
         <v>46229</v>
       </c>
       <c r="P12" s="5" t="s">
@@ -11827,14 +11894,15 @@
         <v>-69</v>
       </c>
       <c r="M13" s="12">
-        <f ca="1">IF($C13="","",$C13+180-TODAY())</f>
+        <f ca="1">IF(AND(TRIM($A13)="Finalized",$K13&lt;&gt;""),"",IF($C13="","",$C13+180-TODAY()))</f>
         <v>147</v>
       </c>
       <c r="N13" s="12">
-        <f ca="1">IF($C13="","",$C13+365-TODAY())</f>
+        <f ca="1">IF(AND(TRIM($A13)="Finalized",$K13&lt;&gt;""),"",IF($C13="","",$C13+365-TODAY()))</f>
         <v>332</v>
       </c>
       <c r="O13" s="6">
+        <f>IF(AND(TRIM($A13)="Finalized",$K13&lt;&gt;""),"",DATE(2026,7,28))</f>
         <v>46231</v>
       </c>
       <c r="P13" s="5" t="s">
@@ -11944,14 +12012,15 @@
         <v>-67</v>
       </c>
       <c r="M14" s="12">
-        <f ca="1">IF($C14="","",$C14+180-TODAY())</f>
+        <f ca="1">IF(AND(TRIM($A14)="Finalized",$K14&lt;&gt;""),"",IF($C14="","",$C14+180-TODAY()))</f>
         <v>100</v>
       </c>
       <c r="N14" s="12">
-        <f ca="1">IF($C14="","",$C14+180-TODAY())</f>
+        <f ca="1">IF(AND(TRIM($A14)="Finalized",$K14&lt;&gt;""),"",IF($C14="","",$C14+180-TODAY()))</f>
         <v>100</v>
       </c>
       <c r="O14" s="6">
+        <f>IF(AND(TRIM($A14)="Finalized",$K14&lt;&gt;""),"",DATE(2026,7,30))</f>
         <v>46233</v>
       </c>
       <c r="P14" s="5" t="s">
@@ -12063,14 +12132,15 @@
         <v>-65</v>
       </c>
       <c r="M15" s="12">
-        <f ca="1">IF($C15="","",$C15+180-TODAY())</f>
+        <f ca="1">IF(AND(TRIM($A15)="Finalized",$K15&lt;&gt;""),"",IF($C15="","",$C15+180-TODAY()))</f>
         <v>16</v>
       </c>
       <c r="N15" s="12">
-        <f ca="1">IF($C15="","",$C15+180-TODAY())</f>
+        <f ca="1">IF(AND(TRIM($A15)="Finalized",$K15&lt;&gt;""),"",IF($C15="","",$C15+180-TODAY()))</f>
         <v>16</v>
       </c>
       <c r="O15" s="6">
+        <f>IF(AND(TRIM($A15)="Finalized",$K15&lt;&gt;""),"",DATE(2026,8,1))</f>
         <v>46235</v>
       </c>
       <c r="P15" s="5" t="s">
@@ -12169,20 +12239,21 @@
       <c r="K16" s="3">
         <v>46269</v>
       </c>
-      <c r="L16" s="12">
+      <c t="str" r="L16" s="12">
         <f ca="1">IF($O16="","",$O16-TODAY())</f>
-        <v>-97</v>
-      </c>
-      <c r="M16" s="12">
-        <f ca="1">IF($C16="","",$C16+180-TODAY())</f>
-        <v>141</v>
-      </c>
-      <c r="N16" s="12">
-        <f ca="1">IF($C16="","",$C16+365-TODAY())</f>
-        <v>326</v>
-      </c>
-      <c r="O16" s="6">
-        <v>46203</v>
+        <v/>
+      </c>
+      <c t="str" r="M16" s="12">
+        <f ca="1">IF(AND(TRIM($A16)="Finalized",$K16&lt;&gt;""),"",IF($C16="","",$C16+180-TODAY()))</f>
+        <v/>
+      </c>
+      <c t="str" r="N16" s="12">
+        <f ca="1">IF(AND(TRIM($A16)="Finalized",$K16&lt;&gt;""),"",IF($C16="","",$C16+365-TODAY()))</f>
+        <v/>
+      </c>
+      <c t="str" r="O16" s="6">
+        <f>IF(AND(TRIM($A16)="Finalized",$K16&lt;&gt;""),"",DATE(2026,6,30))</f>
+        <v/>
       </c>
       <c r="P16" s="5" t="s">
         <v>87</v>
@@ -12282,20 +12353,21 @@
       <c r="K17" s="3">
         <v>46278</v>
       </c>
-      <c r="L17" s="12">
+      <c t="str" r="L17" s="12">
         <f ca="1">IF($O17="","",$O17-TODAY())</f>
-        <v>-85</v>
-      </c>
-      <c r="M17" s="12">
-        <f ca="1">IF($F17="","",$F17+90-TODAY())</f>
-        <v>-85</v>
-      </c>
-      <c r="N17" s="12">
-        <f ca="1">IF($C17="","",$C17+365-TODAY())</f>
-        <v>206</v>
-      </c>
-      <c r="O17" s="6">
-        <v>46215</v>
+        <v/>
+      </c>
+      <c t="str" r="M17" s="12">
+        <f ca="1">IF(AND(TRIM($A17)="Finalized",$K17&lt;&gt;""),"",IF($F17="","",$F17+90-TODAY()))</f>
+        <v/>
+      </c>
+      <c t="str" r="N17" s="12">
+        <f ca="1">IF(AND(TRIM($A17)="Finalized",$K17&lt;&gt;""),"",IF($C17="","",$C17+365-TODAY()))</f>
+        <v/>
+      </c>
+      <c t="str" r="O17" s="6">
+        <f>IF(AND(TRIM($A17)="Finalized",$K17&lt;&gt;""),"",DATE(2026,7,12))</f>
+        <v/>
       </c>
       <c r="P17" s="5" t="s">
         <v>87</v>
@@ -12393,20 +12465,21 @@
       <c r="K18" s="3">
         <v>46278</v>
       </c>
-      <c r="L18" s="12">
+      <c t="str" r="L18" s="12">
         <f ca="1">IF($O18="","",$O18-TODAY())</f>
-        <v>-81</v>
-      </c>
-      <c r="M18" s="12">
-        <f ca="1">IF($C18="","",$C18+180-TODAY())</f>
-        <v>63</v>
-      </c>
-      <c r="N18" s="12">
-        <f ca="1">IF($C18="","",$C18+365-TODAY())</f>
-        <v>248</v>
-      </c>
-      <c r="O18" s="6">
-        <v>46219</v>
+        <v/>
+      </c>
+      <c t="str" r="M18" s="12">
+        <f ca="1">IF(AND(TRIM($A18)="Finalized",$K18&lt;&gt;""),"",IF($C18="","",$C18+180-TODAY()))</f>
+        <v/>
+      </c>
+      <c t="str" r="N18" s="12">
+        <f ca="1">IF(AND(TRIM($A18)="Finalized",$K18&lt;&gt;""),"",IF($C18="","",$C18+365-TODAY()))</f>
+        <v/>
+      </c>
+      <c t="str" r="O18" s="6">
+        <f>IF(AND(TRIM($A18)="Finalized",$K18&lt;&gt;""),"",DATE(2026,7,16))</f>
+        <v/>
       </c>
       <c r="P18" s="5" t="s">
         <v>87</v>
@@ -12472,100 +12545,105 @@
     </row>
   </sheetData>
   <autoFilter ref="A1:AN18" xr:uid="{00000000-0009-0000-0000-000003000000}"/>
+  <conditionalFormatting sqref="L2:O1000">
+    <cfRule type="expression" dxfId="101" priority="1" stopIfTrue="1">
+      <formula>AND(TRIM($A2)="Finalized",$K2&lt;&gt;"")</formula>
+    </cfRule>
+  </conditionalFormatting>
   <conditionalFormatting sqref="L2:L18">
-    <cfRule type="expression" dxfId="39" priority="1">
+    <cfRule type="expression" dxfId="39" priority="2">
       <formula>AND($L2&lt;&gt;"", $L2&gt;=0, $L2&lt;=5)</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="38" priority="2">
+    <cfRule type="expression" dxfId="38" priority="3">
       <formula>AND($L2&lt;&gt;"", $L2&gt;5, $L2&lt;=30)</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="37" priority="3">
+    <cfRule type="expression" dxfId="37" priority="4">
       <formula>AND($L2&lt;&gt;"", $L2&gt;30)</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="36" priority="4">
+    <cfRule type="expression" dxfId="36" priority="5">
       <formula>AND($L2&lt;&gt;"", $L2&lt;0)</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="35" priority="5">
+    <cfRule type="expression" dxfId="35" priority="6">
       <formula>$L2=""</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="M2:M18">
-    <cfRule type="expression" dxfId="34" priority="6">
+    <cfRule type="expression" dxfId="34" priority="7">
       <formula>AND($M2&lt;&gt;"", $M2&gt;=0, $M2&lt;=5)</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="33" priority="7">
+    <cfRule type="expression" dxfId="33" priority="8">
       <formula>AND($M2&lt;&gt;"", $M2&gt;5, $M2&lt;=30)</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="32" priority="8">
+    <cfRule type="expression" dxfId="32" priority="9">
       <formula>AND($M2&lt;&gt;"", $M2&gt;30)</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="31" priority="9">
+    <cfRule type="expression" dxfId="31" priority="10">
       <formula>AND($M2&lt;&gt;"", $M2&lt;0)</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="30" priority="10">
+    <cfRule type="expression" dxfId="30" priority="11">
       <formula>$M2=""</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="N2:N18">
-    <cfRule type="expression" dxfId="29" priority="11">
+    <cfRule type="expression" dxfId="29" priority="12">
       <formula>AND($N2&lt;&gt;"", $N2&gt;=0, $N2&lt;=5)</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="28" priority="12">
+    <cfRule type="expression" dxfId="28" priority="13">
       <formula>AND($N2&lt;&gt;"", $N2&gt;5, $N2&lt;=30)</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="27" priority="13">
+    <cfRule type="expression" dxfId="27" priority="14">
       <formula>AND($N2&lt;&gt;"", $N2&gt;30)</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="26" priority="14">
+    <cfRule type="expression" dxfId="26" priority="15">
       <formula>AND($N2&lt;&gt;"", $N2&lt;0)</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="25" priority="15">
+    <cfRule type="expression" dxfId="25" priority="16">
       <formula>$N2=""</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="O2:U18">
-    <cfRule type="expression" dxfId="24" priority="16">
+    <cfRule type="expression" dxfId="24" priority="17">
       <formula>AND($L2&lt;&gt;"", $L2&gt;=0, $L2&lt;=5)</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="23" priority="17">
+    <cfRule type="expression" dxfId="23" priority="18">
       <formula>AND($L2&lt;&gt;"", $L2&gt;5, $L2&lt;=30)</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="22" priority="18">
+    <cfRule type="expression" dxfId="22" priority="19">
       <formula>AND($L2&lt;&gt;"", $L2&gt;30)</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="21" priority="19">
+    <cfRule type="expression" dxfId="21" priority="20">
       <formula>AND($L2&lt;&gt;"", $L2&lt;0)</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="20" priority="20">
+    <cfRule type="expression" dxfId="20" priority="21">
       <formula>$L2=""</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A2:AN1000">
-    <cfRule type="expression" dxfId="100" priority="21">
+    <cfRule type="expression" dxfId="100" priority="22">
       <formula>TRIM($A2)="PAID"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="101" priority="22">
+    <cfRule type="expression" dxfId="101" priority="23">
       <formula>TRIM($A2)="Finalized"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="102" priority="23">
+    <cfRule type="expression" dxfId="102" priority="24">
       <formula>TRIM($A2)="Received"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="103" priority="24">
+    <cfRule type="expression" dxfId="103" priority="25">
       <formula>TRIM($A2)="Pending"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="104" priority="25">
+    <cfRule type="expression" dxfId="104" priority="26">
       <formula>TRIM($A2)="Under Review"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="105" priority="26">
+    <cfRule type="expression" dxfId="105" priority="27">
       <formula>AND(TRIM($A2)="Denied",$K2="")</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="108" priority="29">
+    <cfRule type="expression" dxfId="108" priority="30">
       <formula>AND(TRIM($A2)="Denied",$K2&lt;&gt;"")</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="106" priority="27">
+    <cfRule type="expression" dxfId="106" priority="28">
       <formula>TRIM($A2)="Rejected"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="107" priority="28">
+    <cfRule type="expression" dxfId="107" priority="29">
       <formula>TRIM($A2)="Not found"</formula>
     </cfRule>
   </conditionalFormatting>
@@ -12780,14 +12858,15 @@
         <v>-75</v>
       </c>
       <c r="M2" s="12">
-        <f ca="1">IF($C2="","",$C2+180-TODAY())</f>
+        <f ca="1">IF(AND(TRIM($A2)="Finalized",$K2&lt;&gt;""),"",IF($C2="","",$C2+180-TODAY()))</f>
         <v>57</v>
       </c>
       <c r="N2" s="12">
-        <f ca="1">IF($C2="","",$C2+365-TODAY())</f>
+        <f ca="1">IF(AND(TRIM($A2)="Finalized",$K2&lt;&gt;""),"",IF($C2="","",$C2+365-TODAY()))</f>
         <v>242</v>
       </c>
       <c r="O2" s="6">
+        <f>IF(AND(TRIM($A2)="Finalized",$K2&lt;&gt;""),"",DATE(2026,7,22))</f>
         <v>46225</v>
       </c>
       <c r="P2" s="5" t="s">
@@ -12889,14 +12968,15 @@
         <v>-68</v>
       </c>
       <c r="M3" s="12">
-        <f ca="1">IF($C3="","",$C3+365-TODAY())</f>
+        <f ca="1">IF(AND(TRIM($A3)="Finalized",$K3&lt;&gt;""),"",IF($C3="","",$C3+365-TODAY()))</f>
         <v>217</v>
       </c>
       <c r="N3" s="12">
-        <f ca="1">IF($C3="","",$C3+365-TODAY())</f>
+        <f ca="1">IF(AND(TRIM($A3)="Finalized",$K3&lt;&gt;""),"",IF($C3="","",$C3+365-TODAY()))</f>
         <v>217</v>
       </c>
       <c r="O3" s="6">
+        <f>IF(AND(TRIM($A3)="Finalized",$K3&lt;&gt;""),"",DATE(2026,7,29))</f>
         <v>46232</v>
       </c>
       <c r="P3" s="5" t="s">
@@ -13001,10 +13081,11 @@
       </c>
       <c r="M4" s="12"/>
       <c r="N4" s="12">
-        <f ca="1">IF($C4="","",$C4+65-TODAY())</f>
+        <f ca="1">IF(AND(TRIM($A4)="Finalized",$K4&lt;&gt;""),"",IF($C4="","",$C4+65-TODAY()))</f>
         <v>-82</v>
       </c>
       <c r="O4" s="6">
+        <f>IF(AND(TRIM($A4)="Finalized",$K4&lt;&gt;""),"",DATE(2026,7,30))</f>
         <v>46233</v>
       </c>
       <c r="P4" s="5" t="s">
@@ -13109,7 +13190,7 @@
       </c>
       <c r="M5" s="12"/>
       <c r="N5" s="12">
-        <f ca="1">IF($C5="","",$C5+180-TODAY())</f>
+        <f ca="1">IF(AND(TRIM($A5)="Finalized",$K5&lt;&gt;""),"",IF($C5="","",$C5+180-TODAY()))</f>
         <v>37</v>
       </c>
       <c r="O5" s="6"/>
@@ -13212,14 +13293,15 @@
         <v>-40</v>
       </c>
       <c r="M6" s="12">
-        <f ca="1">IF($C6="","",$C6+180-TODAY())</f>
+        <f ca="1">IF(AND(TRIM($A6)="Finalized",$K6&lt;&gt;""),"",IF($C6="","",$C6+180-TODAY()))</f>
         <v>44</v>
       </c>
       <c r="N6" s="12">
-        <f ca="1">IF($C6="","",$C6+180-TODAY())</f>
+        <f ca="1">IF(AND(TRIM($A6)="Finalized",$K6&lt;&gt;""),"",IF($C6="","",$C6+180-TODAY()))</f>
         <v>44</v>
       </c>
       <c r="O6" s="6">
+        <f>IF(AND(TRIM($A6)="Finalized",$K6&lt;&gt;""),"",DATE(2026,8,26))</f>
         <v>46260</v>
       </c>
       <c r="P6" s="5" t="s">
@@ -13327,14 +13409,15 @@
         <v>-39</v>
       </c>
       <c r="M7" s="12">
-        <f ca="1">IF($C7="","",$C7+180-TODAY())</f>
+        <f ca="1">IF(AND(TRIM($A7)="Finalized",$K7&lt;&gt;""),"",IF($C7="","",$C7+180-TODAY()))</f>
         <v>65</v>
       </c>
       <c r="N7" s="12">
-        <f ca="1">IF($C7="","",$C7+180-TODAY())</f>
+        <f ca="1">IF(AND(TRIM($A7)="Finalized",$K7&lt;&gt;""),"",IF($C7="","",$C7+180-TODAY()))</f>
         <v>65</v>
       </c>
       <c r="O7" s="6">
+        <f>IF(AND(TRIM($A7)="Finalized",$K7&lt;&gt;""),"",DATE(2026,8,27))</f>
         <v>46261</v>
       </c>
       <c r="P7" s="5" t="s">
@@ -13438,14 +13521,15 @@
         <v>-38</v>
       </c>
       <c r="M8" s="12">
-        <f ca="1">IF($F8="","",$F8+365-TODAY())</f>
+        <f ca="1">IF(AND(TRIM($A8)="Finalized",$K8&lt;&gt;""),"",IF($F8="","",$F8+365-TODAY()))</f>
         <v>207</v>
       </c>
       <c r="N8" s="12" t="str">
-        <f ca="1">IF($C8="","",$C8+180-TODAY())</f>
+        <f ca="1">IF(AND(TRIM($A8)="Finalized",$K8&lt;&gt;""),"",IF($C8="","",$C8+180-TODAY()))</f>
         <v/>
       </c>
       <c r="O8" s="6">
+        <f>IF(AND(TRIM($A8)="Finalized",$K8&lt;&gt;""),"",DATE(2026,8,28))</f>
         <v>46262</v>
       </c>
       <c r="P8" s="5" t="s">
@@ -13549,14 +13633,15 @@
         <v>185</v>
       </c>
       <c r="M9" s="12">
-        <f ca="1">IF($C9="","",$C9+365-TODAY())</f>
+        <f ca="1">IF(AND(TRIM($A9)="Finalized",$K9&lt;&gt;""),"",IF($C9="","",$C9+365-TODAY()))</f>
         <v>222</v>
       </c>
       <c r="N9" s="12">
-        <f ca="1">IF($C9="","",$C9+120-TODAY())</f>
+        <f ca="1">IF(AND(TRIM($A9)="Finalized",$K9&lt;&gt;""),"",IF($C9="","",$C9+120-TODAY()))</f>
         <v>-23</v>
       </c>
       <c r="O9" s="6">
+        <f>IF(AND(TRIM($A9)="Finalized",$K9&lt;&gt;""),"",DATE(2027,4,8))</f>
         <v>46485</v>
       </c>
       <c r="P9" s="5" t="s">
@@ -13662,14 +13747,15 @@
         <v>198</v>
       </c>
       <c r="M10" s="12">
-        <f ca="1">IF($C10="","",$C10+365-TODAY())</f>
+        <f ca="1">IF(AND(TRIM($A10)="Finalized",$K10&lt;&gt;""),"",IF($C10="","",$C10+365-TODAY()))</f>
         <v>235</v>
       </c>
       <c r="N10" s="12">
-        <f ca="1">IF($C10="","",$C10+120-TODAY())</f>
+        <f ca="1">IF(AND(TRIM($A10)="Finalized",$K10&lt;&gt;""),"",IF($C10="","",$C10+120-TODAY()))</f>
         <v>-10</v>
       </c>
       <c r="O10" s="6">
+        <f>IF(AND(TRIM($A10)="Finalized",$K10&lt;&gt;""),"",DATE(2027,4,21))</f>
         <v>46498</v>
       </c>
       <c r="P10" s="5" t="s">
@@ -13779,14 +13865,15 @@
         <v>199</v>
       </c>
       <c r="M11" s="12">
-        <f ca="1">IF($C11="","",$C11+365-TODAY())</f>
+        <f ca="1">IF(AND(TRIM($A11)="Finalized",$K11&lt;&gt;""),"",IF($C11="","",$C11+365-TODAY()))</f>
         <v>220</v>
       </c>
       <c r="N11" s="12">
-        <f ca="1">IF($C11="","",$C11+120-TODAY())</f>
+        <f ca="1">IF(AND(TRIM($A11)="Finalized",$K11&lt;&gt;""),"",IF($C11="","",$C11+120-TODAY()))</f>
         <v>-25</v>
       </c>
       <c r="O11" s="6">
+        <f>IF(AND(TRIM($A11)="Finalized",$K11&lt;&gt;""),"",DATE(2027,4,22))</f>
         <v>46499</v>
       </c>
       <c r="P11" s="5" t="s">
@@ -13896,14 +13983,15 @@
         <v>205</v>
       </c>
       <c r="M12" s="12">
-        <f ca="1">IF($C12="","",$C12+365-TODAY())</f>
+        <f ca="1">IF(AND(TRIM($A12)="Finalized",$K12&lt;&gt;""),"",IF($C12="","",$C12+365-TODAY()))</f>
         <v>219</v>
       </c>
       <c r="N12" s="12">
-        <f ca="1">IF($C12="","",$C12+120-TODAY())</f>
+        <f ca="1">IF(AND(TRIM($A12)="Finalized",$K12&lt;&gt;""),"",IF($C12="","",$C12+120-TODAY()))</f>
         <v>-26</v>
       </c>
       <c r="O12" s="6">
+        <f>IF(AND(TRIM($A12)="Finalized",$K12&lt;&gt;""),"",DATE(2027,4,28))</f>
         <v>46505</v>
       </c>
       <c r="P12" s="5" t="s">
@@ -14007,14 +14095,15 @@
         <v>206</v>
       </c>
       <c r="M13" s="12">
-        <f ca="1">IF($C13="","",$C13+365-TODAY())</f>
+        <f ca="1">IF(AND(TRIM($A13)="Finalized",$K13&lt;&gt;""),"",IF($C13="","",$C13+365-TODAY()))</f>
         <v>219</v>
       </c>
       <c r="N13" s="12">
-        <f ca="1">IF($C13="","",$C13+120-TODAY())</f>
+        <f ca="1">IF(AND(TRIM($A13)="Finalized",$K13&lt;&gt;""),"",IF($C13="","",$C13+120-TODAY()))</f>
         <v>-26</v>
       </c>
       <c r="O13" s="6">
+        <f>IF(AND(TRIM($A13)="Finalized",$K13&lt;&gt;""),"",DATE(2027,4,29))</f>
         <v>46506</v>
       </c>
       <c r="P13" s="5" t="s">
@@ -14118,14 +14207,15 @@
         <v>206</v>
       </c>
       <c r="M14" s="12">
-        <f ca="1">IF($C14="","",$C14+365-TODAY())</f>
+        <f ca="1">IF(AND(TRIM($A14)="Finalized",$K14&lt;&gt;""),"",IF($C14="","",$C14+365-TODAY()))</f>
         <v>219</v>
       </c>
       <c r="N14" s="12">
-        <f ca="1">IF($C14="","",$C14+120-TODAY())</f>
+        <f ca="1">IF(AND(TRIM($A14)="Finalized",$K14&lt;&gt;""),"",IF($C14="","",$C14+120-TODAY()))</f>
         <v>-26</v>
       </c>
       <c r="O14" s="6">
+        <f>IF(AND(TRIM($A14)="Finalized",$K14&lt;&gt;""),"",DATE(2027,4,29))</f>
         <v>46506</v>
       </c>
       <c r="P14" s="5" t="s">
@@ -14229,14 +14319,15 @@
         <v>-96</v>
       </c>
       <c r="M15" s="12">
-        <f ca="1">IF($C15="","",$C15+180-TODAY())</f>
+        <f ca="1">IF(AND(TRIM($A15)="Finalized",$K15&lt;&gt;""),"",IF($C15="","",$C15+180-TODAY()))</f>
         <v>96</v>
       </c>
       <c r="N15" s="12">
-        <f ca="1">IF($C15="","",$C15+365-TODAY())</f>
+        <f ca="1">IF(AND(TRIM($A15)="Finalized",$K15&lt;&gt;""),"",IF($C15="","",$C15+365-TODAY()))</f>
         <v>281</v>
       </c>
       <c r="O15" s="6">
+        <f>IF(AND(TRIM($A15)="Finalized",$K15&lt;&gt;""),"",DATE(2026,7,1))</f>
         <v>46204</v>
       </c>
       <c r="P15" s="5" t="s">
@@ -14344,14 +14435,15 @@
         <v>-91</v>
       </c>
       <c r="M16" s="12">
-        <f ca="1">IF($F16="","",$F16+90-TODAY())</f>
+        <f ca="1">IF(AND(TRIM($A16)="Finalized",$K16&lt;&gt;""),"",IF($F16="","",$F16+90-TODAY()))</f>
         <v>-91</v>
       </c>
       <c r="N16" s="12">
-        <f ca="1">IF($C16="","",$C16+365-TODAY())</f>
+        <f ca="1">IF(AND(TRIM($A16)="Finalized",$K16&lt;&gt;""),"",IF($C16="","",$C16+365-TODAY()))</f>
         <v>229</v>
       </c>
       <c r="O16" s="6">
+        <f>IF(AND(TRIM($A16)="Finalized",$K16&lt;&gt;""),"",DATE(2026,7,6))</f>
         <v>46209</v>
       </c>
       <c r="P16" s="5" t="s">
@@ -14455,14 +14547,15 @@
         <v>-89</v>
       </c>
       <c r="M17" s="12">
-        <f ca="1">IF($C17="","",$C17+180-TODAY())</f>
+        <f ca="1">IF(AND(TRIM($A17)="Finalized",$K17&lt;&gt;""),"",IF($C17="","",$C17+180-TODAY()))</f>
         <v>64</v>
       </c>
       <c r="N17" s="12">
-        <f ca="1">IF($C17="","",$C17+365-TODAY())</f>
+        <f ca="1">IF(AND(TRIM($A17)="Finalized",$K17&lt;&gt;""),"",IF($C17="","",$C17+365-TODAY()))</f>
         <v>249</v>
       </c>
       <c r="O17" s="6">
+        <f>IF(AND(TRIM($A17)="Finalized",$K17&lt;&gt;""),"",DATE(2026,7,8))</f>
         <v>46211</v>
       </c>
       <c r="P17" s="5" t="s">
@@ -14568,14 +14661,15 @@
         <v>-89</v>
       </c>
       <c r="M18" s="12">
-        <f ca="1">IF($C18="","",$C18+180-TODAY())</f>
+        <f ca="1">IF(AND(TRIM($A18)="Finalized",$K18&lt;&gt;""),"",IF($C18="","",$C18+180-TODAY()))</f>
         <v>104</v>
       </c>
       <c r="N18" s="12">
-        <f ca="1">IF($C18="","",$C18+365-TODAY())</f>
+        <f ca="1">IF(AND(TRIM($A18)="Finalized",$K18&lt;&gt;""),"",IF($C18="","",$C18+365-TODAY()))</f>
         <v>289</v>
       </c>
       <c r="O18" s="6">
+        <f>IF(AND(TRIM($A18)="Finalized",$K18&lt;&gt;""),"",DATE(2026,7,8))</f>
         <v>46211</v>
       </c>
       <c r="P18" s="5" t="s">
@@ -14679,14 +14773,15 @@
         <v>-68</v>
       </c>
       <c r="M19" s="12">
-        <f ca="1">IF($C19="","",$C19+180-TODAY())</f>
+        <f ca="1">IF(AND(TRIM($A19)="Finalized",$K19&lt;&gt;""),"",IF($C19="","",$C19+180-TODAY()))</f>
         <v>40</v>
       </c>
       <c r="N19" s="12">
-        <f ca="1">IF($C19="","",$C19+365-TODAY())</f>
+        <f ca="1">IF(AND(TRIM($A19)="Finalized",$K19&lt;&gt;""),"",IF($C19="","",$C19+365-TODAY()))</f>
         <v>225</v>
       </c>
       <c r="O19" s="6">
+        <f>IF(AND(TRIM($A19)="Finalized",$K19&lt;&gt;""),"",DATE(2026,7,29))</f>
         <v>46232</v>
       </c>
       <c r="P19" s="5" t="s">
@@ -14789,20 +14884,21 @@
       <c r="K20" s="3">
         <v>46245</v>
       </c>
-      <c r="L20" s="12">
+      <c t="str" r="L20" s="12">
         <f ca="1">IF($O20="","",$O20-TODAY())</f>
-        <v>-54</v>
-      </c>
-      <c r="M20" s="12">
-        <f ca="1">IF($C20="","",$C20+180-TODAY())</f>
-        <v>79</v>
-      </c>
-      <c r="N20" s="12">
-        <f ca="1">IF($C20="","",$C20+180-TODAY())</f>
-        <v>79</v>
-      </c>
-      <c r="O20" s="6">
-        <v>46246</v>
+        <v/>
+      </c>
+      <c t="str" r="M20" s="12">
+        <f ca="1">IF(AND(TRIM($A20)="Finalized",$K20&lt;&gt;""),"",IF($C20="","",$C20+180-TODAY()))</f>
+        <v/>
+      </c>
+      <c t="str" r="N20" s="12">
+        <f ca="1">IF(AND(TRIM($A20)="Finalized",$K20&lt;&gt;""),"",IF($C20="","",$C20+180-TODAY()))</f>
+        <v/>
+      </c>
+      <c t="str" r="O20" s="6">
+        <f>IF(AND(TRIM($A20)="Finalized",$K20&lt;&gt;""),"",DATE(2026,8,12))</f>
+        <v/>
       </c>
       <c r="P20" s="5" t="s">
         <v>70</v>
@@ -14870,100 +14966,105 @@
     </row>
   </sheetData>
   <autoFilter ref="A1:AN20" xr:uid="{00000000-0009-0000-0000-000004000000}"/>
+  <conditionalFormatting sqref="L2:O1000">
+    <cfRule type="expression" dxfId="101" priority="1" stopIfTrue="1">
+      <formula>AND(TRIM($A2)="Finalized",$K2&lt;&gt;"")</formula>
+    </cfRule>
+  </conditionalFormatting>
   <conditionalFormatting sqref="L2:L20">
-    <cfRule type="expression" dxfId="19" priority="1">
+    <cfRule type="expression" dxfId="19" priority="2">
       <formula>AND($L2&lt;&gt;"", $L2&gt;=0, $L2&lt;=5)</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="18" priority="2">
+    <cfRule type="expression" dxfId="18" priority="3">
       <formula>AND($L2&lt;&gt;"", $L2&gt;5, $L2&lt;=30)</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="17" priority="3">
+    <cfRule type="expression" dxfId="17" priority="4">
       <formula>AND($L2&lt;&gt;"", $L2&gt;30)</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="16" priority="4">
+    <cfRule type="expression" dxfId="16" priority="5">
       <formula>AND($L2&lt;&gt;"", $L2&lt;0)</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="15" priority="5">
+    <cfRule type="expression" dxfId="15" priority="6">
       <formula>$L2=""</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="M2:M20">
-    <cfRule type="expression" dxfId="14" priority="6">
+    <cfRule type="expression" dxfId="14" priority="7">
       <formula>AND($M2&lt;&gt;"", $M2&gt;=0, $M2&lt;=5)</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="13" priority="7">
+    <cfRule type="expression" dxfId="13" priority="8">
       <formula>AND($M2&lt;&gt;"", $M2&gt;5, $M2&lt;=30)</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="12" priority="8">
+    <cfRule type="expression" dxfId="12" priority="9">
       <formula>AND($M2&lt;&gt;"", $M2&gt;30)</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="11" priority="9">
+    <cfRule type="expression" dxfId="11" priority="10">
       <formula>AND($M2&lt;&gt;"", $M2&lt;0)</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="10" priority="10">
+    <cfRule type="expression" dxfId="10" priority="11">
       <formula>$M2=""</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="N2:N20">
-    <cfRule type="expression" dxfId="9" priority="11">
+    <cfRule type="expression" dxfId="9" priority="12">
       <formula>AND($N2&lt;&gt;"", $N2&gt;=0, $N2&lt;=5)</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="8" priority="12">
+    <cfRule type="expression" dxfId="8" priority="13">
       <formula>AND($N2&lt;&gt;"", $N2&gt;5, $N2&lt;=30)</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="7" priority="13">
+    <cfRule type="expression" dxfId="7" priority="14">
       <formula>AND($N2&lt;&gt;"", $N2&gt;30)</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="6" priority="14">
+    <cfRule type="expression" dxfId="6" priority="15">
       <formula>AND($N2&lt;&gt;"", $N2&lt;0)</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="5" priority="15">
+    <cfRule type="expression" dxfId="5" priority="16">
       <formula>$N2=""</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="O2:U20">
-    <cfRule type="expression" dxfId="4" priority="16">
+    <cfRule type="expression" dxfId="4" priority="17">
       <formula>AND($L2&lt;&gt;"", $L2&gt;=0, $L2&lt;=5)</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="3" priority="17">
+    <cfRule type="expression" dxfId="3" priority="18">
       <formula>AND($L2&lt;&gt;"", $L2&gt;5, $L2&lt;=30)</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="2" priority="18">
+    <cfRule type="expression" dxfId="2" priority="19">
       <formula>AND($L2&lt;&gt;"", $L2&gt;30)</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="1" priority="19">
+    <cfRule type="expression" dxfId="1" priority="20">
       <formula>AND($L2&lt;&gt;"", $L2&lt;0)</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="0" priority="20">
+    <cfRule type="expression" dxfId="0" priority="21">
       <formula>$L2=""</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A2:AN1000">
-    <cfRule type="expression" dxfId="100" priority="21">
+    <cfRule type="expression" dxfId="100" priority="22">
       <formula>TRIM($A2)="PAID"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="101" priority="22">
+    <cfRule type="expression" dxfId="101" priority="23">
       <formula>TRIM($A2)="Finalized"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="102" priority="23">
+    <cfRule type="expression" dxfId="102" priority="24">
       <formula>TRIM($A2)="Received"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="103" priority="24">
+    <cfRule type="expression" dxfId="103" priority="25">
       <formula>TRIM($A2)="Pending"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="104" priority="25">
+    <cfRule type="expression" dxfId="104" priority="26">
       <formula>TRIM($A2)="Under Review"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="105" priority="26">
+    <cfRule type="expression" dxfId="105" priority="27">
       <formula>AND(TRIM($A2)="Denied",$K2="")</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="108" priority="29">
+    <cfRule type="expression" dxfId="108" priority="30">
       <formula>AND(TRIM($A2)="Denied",$K2&lt;&gt;"")</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="106" priority="27">
+    <cfRule type="expression" dxfId="106" priority="28">
       <formula>TRIM($A2)="Rejected"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="107" priority="28">
+    <cfRule type="expression" dxfId="107" priority="29">
       <formula>TRIM($A2)="Not found"</formula>
     </cfRule>
   </conditionalFormatting>
